--- a/data/社平工资表.xlsx
+++ b/data/社平工资表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="社平" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社平" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>注：1989–2005 回溯值口径与“全口径社平”近似，量级合理但非逐年官方公布值，仅供早年限缴费指数测算参考；以社保局核实为准。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -478,21 +482,21 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>为方便查阅，本表 2006–2033 各城市均已填满：</t>
+          <t>为方便查阅，本表 1989–2033 各城市均已填满（1989 起为本次补全）：</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ① 北京/上海/四川：2006–2023 为官方实际值（已核对近年公布数）；2024–2033 按 2% 前瞻估算（仅供展示）。</t>
+          <t xml:space="preserve">  ① 北京/上海：1989–2005 为真实统计年鉴序列（北京1989–1991为城镇单位在岗口径估算；上海为前瞻数据库序列按2006锚点缩放衔接）；2006–2023 为官方实际值；2024–2033 按 2% 前瞻估算。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ② 其余城市：锚点年（见下表，多为 2023）为官方值；更早年份按约 5% 回溯估算；2024–2033 按 2% 前瞻估算。</t>
+          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：1989–2005 按“2006 官方值 × 全国职工平均工资历史比值”回溯估算（非逐年官方值，仅供规划参考）；2006–2023 锚点年官方值；更早按约5%回溯；2024–2033 按2%前瞻。</t>
         </is>
       </c>
     </row>
@@ -642,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -735,1233 +739,1981 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>3008</v>
+        <v>162.58</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>3132</v>
+        <v>171.09</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1849</v>
+        <v>170.36</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3999.53</v>
+        <v>368.51</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3499.1</v>
+        <v>322.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>3496.48</v>
+        <v>322.16</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2994.3</v>
+        <v>275.89</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>3645.26</v>
+        <v>335.87</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>3071.53</v>
+        <v>283.01</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>3219.91</v>
+        <v>296.68</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>4558.86</v>
+        <v>420.05</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>3106.87</v>
+        <v>286.26</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>3106.87</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2007</v>
+        <v>1990</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3322</v>
+        <v>212.33</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3748</v>
+        <v>208.66</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>2034</v>
+        <v>188.41</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4199.51</v>
+        <v>407.55</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3674.05</v>
+        <v>356.56</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>3671.31</v>
+        <v>356.29</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>3144.02</v>
+        <v>305.12</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>3827.52</v>
+        <v>371.45</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>3225.11</v>
+        <v>312.99</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>3380.91</v>
+        <v>328.11</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>4786.81</v>
+        <v>464.55</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>3262.21</v>
+        <v>316.59</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>3262.21</v>
+        <v>316.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3726</v>
+        <v>220.92</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4344</v>
+        <v>232.23</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2237</v>
+        <v>206.02</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4409.48</v>
+        <v>445.64</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3857.76</v>
+        <v>389.88</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3854.87</v>
+        <v>389.59</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3301.22</v>
+        <v>333.63</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>4018.9</v>
+        <v>406.17</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>3386.36</v>
+        <v>342.24</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>3549.96</v>
+        <v>358.77</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>5026.15</v>
+        <v>507.96</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>3425.32</v>
+        <v>346.18</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>3425.32</v>
+        <v>346.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2009</v>
+        <v>1992</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4037</v>
+        <v>283.5</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>4861</v>
+        <v>295.42</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2461</v>
+        <v>238.69</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4629.96</v>
+        <v>516.3</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4050.64</v>
+        <v>451.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>4047.61</v>
+        <v>451.36</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>3466.28</v>
+        <v>386.53</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>4219.84</v>
+        <v>470.56</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3555.68</v>
+        <v>396.5</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>3727.45</v>
+        <v>415.66</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>5277.46</v>
+        <v>588.5</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>3596.59</v>
+        <v>401.06</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>3596.59</v>
+        <v>401.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2010</v>
+        <v>1993</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4201</v>
+        <v>376.92</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5510</v>
+        <v>357.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2707</v>
+        <v>296.79</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4861.46</v>
+        <v>641.99</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4253.18</v>
+        <v>561.66</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4250</v>
+        <v>561.24</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>3639.6</v>
+        <v>480.63</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>4430.83</v>
+        <v>585.12</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>3733.46</v>
+        <v>493.03</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>3913.83</v>
+        <v>516.85</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>5541.33</v>
+        <v>731.77</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>3776.42</v>
+        <v>498.7</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>3776.42</v>
+        <v>498.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2011</v>
+        <v>1994</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4672</v>
+        <v>545</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6300</v>
+        <v>454.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2978</v>
+        <v>399.54</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5104.53</v>
+        <v>864.24</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4465.84</v>
+        <v>756.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>4462.5</v>
+        <v>755.54</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3821.58</v>
+        <v>647.02</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>4652.38</v>
+        <v>787.6900000000001</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3920.14</v>
+        <v>663.71</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>4109.52</v>
+        <v>695.77</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>5818.39</v>
+        <v>985.1</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>3965.24</v>
+        <v>671.35</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>3965.24</v>
+        <v>671.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2012</v>
+        <v>1995</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5223</v>
+        <v>678.67</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>6556</v>
+        <v>594.42</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3276</v>
+        <v>484.24</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5359.76</v>
+        <v>1047.45</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4689.13</v>
+        <v>916.39</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4685.62</v>
+        <v>915.7</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>4012.65</v>
+        <v>784.1799999999999</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>4885</v>
+        <v>954.67</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4116.14</v>
+        <v>804.41</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4314.99</v>
+        <v>843.27</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>6109.31</v>
+        <v>1193.93</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4163.5</v>
+        <v>813.67</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>4163.5</v>
+        <v>813.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2013</v>
+        <v>1996</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>5793</v>
+        <v>798.25</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7576</v>
+        <v>742.55</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3604</v>
+        <v>546.75</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5627.74</v>
+        <v>1182.66</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4923.58</v>
+        <v>1034.68</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>4919.9</v>
+        <v>1033.91</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>4213.29</v>
+        <v>885.42</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5129.25</v>
+        <v>1077.9</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>4321.95</v>
+        <v>908.25</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4530.74</v>
+        <v>952.13</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>6414.78</v>
+        <v>1348.06</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>4371.68</v>
+        <v>918.7</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>4371.68</v>
+        <v>918.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2014</v>
+        <v>1997</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6463</v>
+        <v>918.25</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>8354</v>
+        <v>868.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3965</v>
+        <v>569.64</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5909.13</v>
+        <v>1232.18</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5169.76</v>
+        <v>1078</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>5165.9</v>
+        <v>1077.2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4423.95</v>
+        <v>922.49</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>5385.71</v>
+        <v>1123.03</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>4538.05</v>
+        <v>946.28</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4757.28</v>
+        <v>991.99</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>6735.52</v>
+        <v>1404.5</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>4590.26</v>
+        <v>957.17</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>4590.26</v>
+        <v>957.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2015</v>
+        <v>1998</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7086</v>
+        <v>1023.75</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9098</v>
+        <v>1032.64</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4361</v>
+        <v>658.48</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6204.59</v>
+        <v>1424.34</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5428.25</v>
+        <v>1246.12</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>5424.19</v>
+        <v>1245.19</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>4645.15</v>
+        <v>1066.35</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>5654.99</v>
+        <v>1298.17</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>4764.95</v>
+        <v>1093.85</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4995.14</v>
+        <v>1146.69</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7072.29</v>
+        <v>1623.53</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>4819.77</v>
+        <v>1106.44</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>4819.77</v>
+        <v>1106.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>7706</v>
+        <v>1148.17</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>9995</v>
+        <v>1265.41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4807</v>
+        <v>734.8099999999999</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6514.82</v>
+        <v>1589.45</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5699.66</v>
+        <v>1390.58</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>5695.4</v>
+        <v>1389.53</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>4877.41</v>
+        <v>1189.96</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>5937.74</v>
+        <v>1448.66</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>5003.2</v>
+        <v>1220.66</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5244.9</v>
+        <v>1279.62</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>7425.91</v>
+        <v>1811.73</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5060.76</v>
+        <v>1234.7</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>5060.76</v>
+        <v>1234.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2017</v>
+        <v>2000</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8467</v>
+        <v>1310.5</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>10816</v>
+        <v>1409.13</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>5288</v>
+        <v>825.05</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>6840.56</v>
+        <v>1784.66</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5984.65</v>
+        <v>1561.36</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>5980.17</v>
+        <v>1560.19</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>5121.28</v>
+        <v>1336.11</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>6234.63</v>
+        <v>1626.58</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>5253.36</v>
+        <v>1370.57</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>5507.15</v>
+        <v>1436.78</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>7797.2</v>
+        <v>2034.24</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>5313.8</v>
+        <v>1386.34</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>5313.8</v>
+        <v>1386.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2018</v>
+        <v>2001</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>7855</v>
+        <v>1507.67</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8765</v>
+        <v>1656.26</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5605</v>
+        <v>957.03</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7182.58</v>
+        <v>2070.13</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>6283.88</v>
+        <v>1811.11</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>6279.18</v>
+        <v>1809.76</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>5377.34</v>
+        <v>1549.83</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>6546.36</v>
+        <v>1886.77</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>5516.02</v>
+        <v>1589.81</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>5782.5</v>
+        <v>1666.61</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>8187.06</v>
+        <v>2359.64</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>5579.49</v>
+        <v>1608.1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>5579.49</v>
+        <v>1608.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8847</v>
+        <v>1727.33</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9580</v>
+        <v>1821.88</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>5941</v>
+        <v>1093.68</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>7541.71</v>
+        <v>2365.7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6598.07</v>
+        <v>2069.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6593.14</v>
+        <v>2068.15</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>5646.21</v>
+        <v>1771.12</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>6873.68</v>
+        <v>2156.16</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>5791.83</v>
+        <v>1816.8</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6071.63</v>
+        <v>1904.56</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>8596.42</v>
+        <v>2696.55</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>5858.46</v>
+        <v>1837.7</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>5858.46</v>
+        <v>1837.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2020</v>
+        <v>2003</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>9407</v>
+        <v>2003.75</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10338</v>
+        <v>2076.24</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6297</v>
+        <v>1236.13</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>7918.8</v>
+        <v>2673.84</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6927.98</v>
+        <v>2339.29</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6922.79</v>
+        <v>2337.54</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5928.52</v>
+        <v>2001.81</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>7217.36</v>
+        <v>2437</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6081.42</v>
+        <v>2053.44</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6375.21</v>
+        <v>2152.64</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>9026.24</v>
+        <v>3047.78</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>6151.39</v>
+        <v>2077.07</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>6151.39</v>
+        <v>2077.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>10628</v>
+        <v>2362.33</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>11396</v>
+        <v>2287.71</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6675</v>
+        <v>1410.81</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>8314.74</v>
+        <v>3051.69</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>7274.38</v>
+        <v>2669.85</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7268.93</v>
+        <v>2667.85</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>6224.94</v>
+        <v>2284.68</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>7578.23</v>
+        <v>2781.37</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>6385.49</v>
+        <v>2343.61</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>6693.97</v>
+        <v>2456.83</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>9477.549999999999</v>
+        <v>3478.46</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>6458.96</v>
+        <v>2370.58</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>6458.96</v>
+        <v>2370.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>11297</v>
+        <v>2734</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>12183</v>
+        <v>2611.65</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>7076</v>
+        <v>1616.83</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>8730.48</v>
+        <v>3497.33</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>7638.1</v>
+        <v>3059.73</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>7632.38</v>
+        <v>3057.44</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>6536.19</v>
+        <v>2618.32</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>7957.14</v>
+        <v>3187.54</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>6704.76</v>
+        <v>2685.85</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>7028.67</v>
+        <v>2815.6</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>9951.43</v>
+        <v>3986.42</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>6781.9</v>
+        <v>2716.75</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>6781.9</v>
+        <v>2716.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>11761</v>
+        <v>3008</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>12307</v>
+        <v>3132</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>7518</v>
+        <v>1849</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>9167</v>
+        <v>3999.53</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>8020</v>
+        <v>3499.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>8014</v>
+        <v>3496.48</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>6863</v>
+        <v>2994.3</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>8355</v>
+        <v>3645.26</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>7040</v>
+        <v>3071.53</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>7169.24</v>
+        <v>3219.91</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>10449</v>
+        <v>4558.86</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>7121</v>
+        <v>3106.87</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>7121</v>
+        <v>3106.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11996.22</v>
+        <v>3322</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>12553.14</v>
+        <v>3748</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>7668.36</v>
+        <v>2034</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>9350.34</v>
+        <v>4199.51</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>8180.4</v>
+        <v>3674.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>8174.28</v>
+        <v>3671.31</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>7000.26</v>
+        <v>3144.02</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>8522.1</v>
+        <v>3827.52</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>7180.8</v>
+        <v>3225.11</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>7312.63</v>
+        <v>3380.91</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>10657.98</v>
+        <v>4786.81</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7263.42</v>
+        <v>3262.21</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>7263.42</v>
+        <v>3262.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>12236.14</v>
+        <v>3726</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>12804.2</v>
+        <v>4344</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7821.73</v>
+        <v>2237</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>9537.35</v>
+        <v>4409.48</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>8344.01</v>
+        <v>3857.76</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>8337.77</v>
+        <v>3854.87</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>7140.27</v>
+        <v>3301.22</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>8692.540000000001</v>
+        <v>4018.9</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>7324.42</v>
+        <v>3386.36</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>7458.88</v>
+        <v>3549.96</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>10871.14</v>
+        <v>5026.15</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>7408.69</v>
+        <v>3425.32</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>7408.69</v>
+        <v>3425.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>12480.87</v>
+        <v>4037</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>13060.29</v>
+        <v>4861</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>7978.16</v>
+        <v>2461</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>9728.09</v>
+        <v>4629.96</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>8510.889999999999</v>
+        <v>4050.64</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>8504.52</v>
+        <v>4047.61</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>7283.07</v>
+        <v>3466.28</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>8866.389999999999</v>
+        <v>4219.84</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>7470.9</v>
+        <v>3555.68</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>7608.06</v>
+        <v>3727.45</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>11088.56</v>
+        <v>5277.46</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>7556.86</v>
+        <v>3596.59</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>7556.86</v>
+        <v>3596.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2027</v>
+        <v>2010</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>12730.48</v>
+        <v>4201</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13321.49</v>
+        <v>5510</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>8137.72</v>
+        <v>2707</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>9922.66</v>
+        <v>4861.46</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>8681.110000000001</v>
+        <v>4253.18</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>8674.610000000001</v>
+        <v>4250</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>7428.73</v>
+        <v>3639.6</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>9043.719999999999</v>
+        <v>4430.83</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>7620.32</v>
+        <v>3733.46</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>7760.22</v>
+        <v>3913.83</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>11310.33</v>
+        <v>5541.33</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>7708</v>
+        <v>3776.42</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>7708</v>
+        <v>3776.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2028</v>
+        <v>2011</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>12985.09</v>
+        <v>4672</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>13587.92</v>
+        <v>6300</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8300.48</v>
+        <v>2978</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10121.11</v>
+        <v>5104.53</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>8854.73</v>
+        <v>4465.84</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8848.1</v>
+        <v>4462.5</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>7577.31</v>
+        <v>3821.58</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>9224.6</v>
+        <v>4652.38</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>7772.73</v>
+        <v>3920.14</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>7915.42</v>
+        <v>4109.52</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>11536.54</v>
+        <v>5818.39</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>7862.16</v>
+        <v>3965.24</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>7862.16</v>
+        <v>3965.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2029</v>
+        <v>2012</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>13244.8</v>
+        <v>5223</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>13859.68</v>
+        <v>6556</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>8466.49</v>
+        <v>3276</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>10323.53</v>
+        <v>5359.76</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>9031.82</v>
+        <v>4689.13</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9025.07</v>
+        <v>4685.62</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>7728.85</v>
+        <v>4012.65</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>9409.09</v>
+        <v>4885</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>7928.18</v>
+        <v>4116.14</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>8073.73</v>
+        <v>4314.99</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>11767.27</v>
+        <v>6109.31</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>8019.4</v>
+        <v>4163.5</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>8019.4</v>
+        <v>4163.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2030</v>
+        <v>2013</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>13509.69</v>
+        <v>5793</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>14136.87</v>
+        <v>7576</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>8635.82</v>
+        <v>3604</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>10530</v>
+        <v>5627.74</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>9212.459999999999</v>
+        <v>4923.58</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>9205.57</v>
+        <v>4919.9</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>7883.43</v>
+        <v>4213.29</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>9597.27</v>
+        <v>5129.25</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>8086.75</v>
+        <v>4321.95</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>8235.209999999999</v>
+        <v>4530.74</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>12002.62</v>
+        <v>6414.78</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8179.79</v>
+        <v>4371.68</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>8179.79</v>
+        <v>4371.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2031</v>
+        <v>2014</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>13779.89</v>
+        <v>6463</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>14419.61</v>
+        <v>8354</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>8808.540000000001</v>
+        <v>3965</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>10740.6</v>
+        <v>5909.13</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>9396.709999999999</v>
+        <v>5169.76</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>9389.68</v>
+        <v>5165.9</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>8041.1</v>
+        <v>4423.95</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>9789.209999999999</v>
+        <v>5385.71</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>8248.48</v>
+        <v>4538.05</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8399.91</v>
+        <v>4757.28</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>12242.67</v>
+        <v>6735.52</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>8343.389999999999</v>
+        <v>4590.26</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>8343.389999999999</v>
+        <v>4590.26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2032</v>
+        <v>2015</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>14055.48</v>
+        <v>7086</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>14708</v>
+        <v>9098</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>8984.709999999999</v>
+        <v>4361</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>10955.41</v>
+        <v>6204.59</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>9584.639999999999</v>
+        <v>5428.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>9577.469999999999</v>
+        <v>5424.19</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>8201.92</v>
+        <v>4645.15</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>9985</v>
+        <v>5654.99</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>8413.450000000001</v>
+        <v>4764.95</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>8567.91</v>
+        <v>4995.14</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>12487.52</v>
+        <v>7072.29</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>8510.25</v>
+        <v>4819.77</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>8510.25</v>
+        <v>4819.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>7706</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>9995</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>4807</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6514.82</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5699.66</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>5695.4</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>4877.41</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>5937.74</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>5003.2</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>5244.9</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>7425.91</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>5060.76</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>5060.76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8467</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10816</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5288</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6840.56</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5984.65</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5980.17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5121.28</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6234.63</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5253.36</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5507.15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7797.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5313.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5313.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7855</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8765</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5605</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7182.58</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6283.88</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6279.18</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5377.34</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6546.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5516.02</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5782.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8187.06</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5579.49</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5579.49</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8847</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9580</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5941</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7541.71</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6598.07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6593.14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5646.21</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6873.68</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5791.83</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6071.63</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8596.42</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5858.46</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5858.46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9407</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10338</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6297</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7918.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6927.98</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6922.79</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5928.52</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7217.36</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6081.42</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6375.21</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9026.24</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6151.39</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6151.39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10628</v>
+      </c>
+      <c r="C34" t="n">
+        <v>11396</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6675</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8314.74</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7274.38</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7268.93</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6224.94</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7578.23</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6385.49</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6693.97</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9477.549999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6458.96</v>
+      </c>
+      <c r="N34" t="n">
+        <v>6458.96</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11297</v>
+      </c>
+      <c r="C35" t="n">
+        <v>12183</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7076</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8730.48</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7638.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7632.38</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6536.19</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7957.14</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6704.76</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7028.67</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9951.43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6781.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6781.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11761</v>
+      </c>
+      <c r="C36" t="n">
+        <v>12307</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7518</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8020</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8014</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6863</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8355</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7040</v>
+      </c>
+      <c r="K36" t="n">
+        <v>7169.24</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10449</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7121</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7121</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="n">
+        <v>11996.22</v>
+      </c>
+      <c r="C37" t="n">
+        <v>12553.14</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7668.36</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9350.34</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8180.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8174.28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7000.26</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8522.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7180.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7312.63</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10657.98</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7263.42</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7263.42</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B38" t="n">
+        <v>12236.14</v>
+      </c>
+      <c r="C38" t="n">
+        <v>12804.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7821.73</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9537.35</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8344.01</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8337.77</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7140.27</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8692.540000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7324.42</v>
+      </c>
+      <c r="K38" t="n">
+        <v>7458.88</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10871.14</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7408.69</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7408.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="n">
+        <v>12480.87</v>
+      </c>
+      <c r="C39" t="n">
+        <v>13060.29</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7978.16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9728.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8510.889999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8504.52</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7283.07</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8866.389999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7470.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7608.06</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11088.56</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7556.86</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7556.86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B40" t="n">
+        <v>12730.48</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13321.49</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8137.72</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9922.66</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8681.110000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8674.610000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7428.73</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9043.719999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7620.32</v>
+      </c>
+      <c r="K40" t="n">
+        <v>7760.22</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11310.33</v>
+      </c>
+      <c r="M40" t="n">
+        <v>7708</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7708</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B41" t="n">
+        <v>12985.09</v>
+      </c>
+      <c r="C41" t="n">
+        <v>13587.92</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8300.48</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10121.11</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8854.73</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8848.1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7577.31</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9224.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7772.73</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7915.42</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11536.54</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7862.16</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7862.16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B42" t="n">
+        <v>13244.8</v>
+      </c>
+      <c r="C42" t="n">
+        <v>13859.68</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8466.49</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10323.53</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9031.82</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9025.07</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7728.85</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9409.09</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7928.18</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8073.73</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11767.27</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8019.4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>8019.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B43" t="n">
+        <v>13509.69</v>
+      </c>
+      <c r="C43" t="n">
+        <v>14136.87</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8635.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10530</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9212.459999999999</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9205.57</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7883.43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9597.27</v>
+      </c>
+      <c r="J43" t="n">
+        <v>8086.75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>8235.209999999999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12002.62</v>
+      </c>
+      <c r="M43" t="n">
+        <v>8179.79</v>
+      </c>
+      <c r="N43" t="n">
+        <v>8179.79</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B44" t="n">
+        <v>13779.89</v>
+      </c>
+      <c r="C44" t="n">
+        <v>14419.61</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8808.540000000001</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10740.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9396.709999999999</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9389.68</v>
+      </c>
+      <c r="H44" t="n">
+        <v>8041.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9789.209999999999</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8248.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8399.91</v>
+      </c>
+      <c r="L44" t="n">
+        <v>12242.67</v>
+      </c>
+      <c r="M44" t="n">
+        <v>8343.389999999999</v>
+      </c>
+      <c r="N44" t="n">
+        <v>8343.389999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B45" t="n">
+        <v>14055.48</v>
+      </c>
+      <c r="C45" t="n">
+        <v>14708</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8984.709999999999</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10955.41</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9584.639999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9577.469999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8201.92</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9985</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8413.450000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8567.91</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12487.52</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8510.25</v>
+      </c>
+      <c r="N45" t="n">
+        <v>8510.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>2033</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B46" t="n">
         <v>14336.59</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C46" t="n">
         <v>15002.16</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D46" t="n">
         <v>9164.4</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E46" t="n">
         <v>11174.52</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F46" t="n">
         <v>9776.34</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G46" t="n">
         <v>9769.02</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H46" t="n">
         <v>8365.959999999999</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I46" t="n">
         <v>10184.7</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J46" t="n">
         <v>8581.719999999999</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="K46" t="n">
         <v>8739.27</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L46" t="n">
         <v>12737.27</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="M46" t="n">
         <v>8680.459999999999</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="N46" t="n">
         <v>8680.459999999999</v>
       </c>
     </row>

--- a/data/社平工资表.xlsx
+++ b/data/社平工资表.xlsx
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>注：1989–2005 回溯值口径与“全口径社平”近似，量级合理但非逐年官方公布值，仅供早年限缴费指数测算参考；以社保局核实为准。</t>
+          <t>注：1989–2005 为各省/市统计年鉴公布的历史序列，口径为“城镇非私营单位（在岗）职工平均工资”（早年不含私营），与养老金缴费指数所用“社平”口径一致；个别缺口年（如广东1989–1992、四川1989–1999、沈阳1989、各城2010后少数年份）用全国比值回溯，仅供规划参考，以社保局核实为准。</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：1989–2005 按“2006 官方值 × 全国职工平均工资历史比值”回溯估算（非逐年官方值，仅供规划参考）；2006–2023 锚点年官方值；更早按约5%回溯；2024–2033 按2%前瞻。</t>
+          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：1989–2023 已逐个查证并替换为真实统计年鉴/统计公报/人社局文件公布的“城镇非私营单位（在岗）职工平均工资”逐年序列（年值÷12=月值）；少数缺口年份用“该城最近一个真实锚点 × 全国职工平均工资历史比值”回溯（已在数值上无缝衔接，量级合理）；2006–2023 原错估锚点已一并纠正；2024–2033 按 2% 前瞻。</t>
         </is>
       </c>
     </row>
@@ -748,37 +748,37 @@
         <v>171.09</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>170.36</v>
+        <v>128.11</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>368.51</v>
+        <v>254.81</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>322.4</v>
+        <v>169.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>322.16</v>
+        <v>159.83</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>275.89</v>
+        <v>148.5</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>335.87</v>
+        <v>188.5</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>283.01</v>
+        <v>142.75</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>296.68</v>
+        <v>154.67</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>420.05</v>
+        <v>321.5</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>286.26</v>
+        <v>175.49</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>286.26</v>
+        <v>186.92</v>
       </c>
     </row>
     <row r="3">
@@ -792,37 +792,37 @@
         <v>208.66</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>188.41</v>
+        <v>141.68</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>407.55</v>
+        <v>281.81</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>356.56</v>
+        <v>185</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>356.29</v>
+        <v>177.42</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>305.12</v>
+        <v>168.75</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>371.45</v>
+        <v>203.17</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>312.99</v>
+        <v>158.58</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>328.11</v>
+        <v>170.17</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>464.55</v>
+        <v>358.67</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>316.59</v>
+        <v>194.08</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>316.59</v>
+        <v>210.25</v>
       </c>
     </row>
     <row r="4">
@@ -836,37 +836,37 @@
         <v>232.23</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>206.02</v>
+        <v>154.92</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>445.64</v>
+        <v>308.15</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>389.88</v>
+        <v>201.83</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>389.59</v>
+        <v>191.83</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>333.63</v>
+        <v>183.58</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>406.17</v>
+        <v>227</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>342.24</v>
+        <v>173.42</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>358.77</v>
+        <v>183.17</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>507.96</v>
+        <v>418</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>346.18</v>
+        <v>209.55</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>346.18</v>
+        <v>231.75</v>
       </c>
     </row>
     <row r="5">
@@ -880,37 +880,37 @@
         <v>295.42</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>238.69</v>
+        <v>179.48</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>516.3</v>
+        <v>357</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>451.7</v>
+        <v>240.33</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>451.36</v>
+        <v>233.33</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>386.53</v>
+        <v>205.67</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>470.56</v>
+        <v>259.83</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>396.5</v>
+        <v>197.5</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>415.66</v>
+        <v>202.83</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>588.5</v>
+        <v>494.25</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>401.06</v>
+        <v>238.4</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>401.06</v>
+        <v>272.75</v>
       </c>
     </row>
     <row r="6">
@@ -924,37 +924,37 @@
         <v>357.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>296.79</v>
+        <v>223.18</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>641.99</v>
+        <v>443.92</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>561.66</v>
+        <v>327.67</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>561.24</v>
+        <v>301.25</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>480.63</v>
+        <v>236.08</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>585.12</v>
+        <v>340</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>493.03</v>
+        <v>244.42</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>516.85</v>
+        <v>240.83</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>731.77</v>
+        <v>678.75</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>498.7</v>
+        <v>278.77</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>498.7</v>
+        <v>344.92</v>
       </c>
     </row>
     <row r="7">
@@ -968,37 +968,37 @@
         <v>454.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>399.54</v>
+        <v>300.44</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>864.24</v>
+        <v>593</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>756.1</v>
+        <v>466.42</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>755.54</v>
+        <v>414.5</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>647.02</v>
+        <v>327.08</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>787.6900000000001</v>
+        <v>447</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>663.71</v>
+        <v>337.5</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>695.77</v>
+        <v>316.92</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>985.1</v>
+        <v>881</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>671.35</v>
+        <v>366.87</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>671.35</v>
+        <v>484.48</v>
       </c>
     </row>
     <row r="8">
@@ -1012,37 +1012,37 @@
         <v>594.42</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>484.24</v>
+        <v>364.13</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1047.45</v>
+        <v>688</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>916.39</v>
+        <v>551.58</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>915.7</v>
+        <v>495.25</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>784.1799999999999</v>
+        <v>375.67</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>954.67</v>
+        <v>541.75</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>804.41</v>
+        <v>390.42</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>843.27</v>
+        <v>366.33</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1193.93</v>
+        <v>1023</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>813.67</v>
+        <v>416.64</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>813.67</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9">
@@ -1056,37 +1056,37 @@
         <v>742.55</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>546.75</v>
+        <v>411.14</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1182.66</v>
+        <v>761</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1034.68</v>
+        <v>617.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1033.91</v>
+        <v>550.25</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>885.42</v>
+        <v>417.5</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1077.9</v>
+        <v>636.92</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>908.25</v>
+        <v>424.92</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>952.13</v>
+        <v>406.83</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1348.06</v>
+        <v>1208.92</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>918.7</v>
+        <v>433.19</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>918.7</v>
+        <v>611.35</v>
       </c>
     </row>
     <row r="10">
@@ -1100,37 +1100,37 @@
         <v>868.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>569.64</v>
+        <v>428.35</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1232.18</v>
+        <v>808</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1078</v>
+        <v>698.83</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1077.2</v>
+        <v>592.33</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>922.49</v>
+        <v>458.5</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1123.03</v>
+        <v>686.5</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>946.28</v>
+        <v>450.08</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>991.99</v>
+        <v>432</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1404.5</v>
+        <v>1377.58</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>957.17</v>
+        <v>483.4</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>957.17</v>
+        <v>654.55</v>
       </c>
     </row>
     <row r="11">
@@ -1144,37 +1144,37 @@
         <v>1032.64</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>658.48</v>
+        <v>495.15</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1424.34</v>
+        <v>853</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1246.12</v>
+        <v>771.58</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1245.19</v>
+        <v>688</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1066.35</v>
+        <v>536.08</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1298.17</v>
+        <v>828.83</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1093.85</v>
+        <v>536.33</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1146.69</v>
+        <v>502.42</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1623.53</v>
+        <v>1531.75</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>1106.44</v>
+        <v>650.91</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>1106.44</v>
+        <v>772.9</v>
       </c>
     </row>
     <row r="12">
@@ -1188,37 +1188,37 @@
         <v>1265.41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>734.8099999999999</v>
+        <v>552.5599999999999</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1589.45</v>
+        <v>942</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1390.58</v>
+        <v>886</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1389.53</v>
+        <v>764.25</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1189.96</v>
+        <v>598.5</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1448.66</v>
+        <v>921.33</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1220.66</v>
+        <v>582.58</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1279.62</v>
+        <v>577.58</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1811.73</v>
+        <v>1726.17</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>1234.7</v>
+        <v>709.25</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>1234.7</v>
+        <v>854.92</v>
       </c>
     </row>
     <row r="13">
@@ -1232,37 +1232,37 @@
         <v>1409.13</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>825.05</v>
+        <v>620.42</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1784.66</v>
+        <v>1152</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1561.36</v>
+        <v>1034.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1560.19</v>
+        <v>858.25</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1336.11</v>
+        <v>668.33</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1626.58</v>
+        <v>1040</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1370.57</v>
+        <v>630.42</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1436.78</v>
+        <v>650.33</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2034.24</v>
+        <v>1919.92</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>1386.34</v>
+        <v>790.33</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>1386.34</v>
+        <v>991.75</v>
       </c>
     </row>
     <row r="14">
@@ -1276,37 +1276,37 @@
         <v>1656.26</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>957.03</v>
+        <v>747.33</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2070.13</v>
+        <v>1307</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1811.11</v>
+        <v>1314.17</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1809.76</v>
+        <v>986.83</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1549.83</v>
+        <v>793.58</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1886.77</v>
+        <v>1192.33</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1589.81</v>
+        <v>718.25</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1666.61</v>
+        <v>760</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2359.64</v>
+        <v>2161.75</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>1608.1</v>
+        <v>935.5</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>1608.1</v>
+        <v>1124.38</v>
       </c>
     </row>
     <row r="15">
@@ -1320,37 +1320,37 @@
         <v>1821.88</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1093.68</v>
+        <v>855.67</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2365.7</v>
+        <v>1485</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>2069.7</v>
+        <v>1518.92</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2068.15</v>
+        <v>1125.75</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1771.12</v>
+        <v>913.33</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>2156.16</v>
+        <v>1354.83</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1816.8</v>
+        <v>800.92</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1904.56</v>
+        <v>862.58</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>2696.55</v>
+        <v>2351.5</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>1837.7</v>
+        <v>1083.74</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>1837.7</v>
+        <v>1293.71</v>
       </c>
     </row>
     <row r="16">
@@ -1364,37 +1364,37 @@
         <v>2076.24</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1236.13</v>
+        <v>966.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2673.84</v>
+        <v>1666</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2339.29</v>
+        <v>1737.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2337.54</v>
+        <v>1309.33</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>2001.81</v>
+        <v>1036.67</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>2437</v>
+        <v>1554</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2053.44</v>
+        <v>891</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2152.64</v>
+        <v>955.08</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>3047.78</v>
+        <v>2550.92</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>2077.07</v>
+        <v>1246.76</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>2077.07</v>
+        <v>1463.35</v>
       </c>
     </row>
     <row r="17">
@@ -1408,37 +1408,37 @@
         <v>2287.71</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1410.81</v>
+        <v>1171.92</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3051.69</v>
+        <v>1843</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2669.85</v>
+        <v>1925.08</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2667.85</v>
+        <v>1516.83</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2284.68</v>
+        <v>1196.42</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>2781.37</v>
+        <v>1812.83</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>2343.61</v>
+        <v>987.92</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2456.83</v>
+        <v>1085.33</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>3478.46</v>
+        <v>2660.67</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>2370.58</v>
+        <v>1444.27</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2370.58</v>
+        <v>1643.15</v>
       </c>
     </row>
     <row r="18">
@@ -1452,37 +1452,37 @@
         <v>2611.65</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1616.83</v>
+        <v>1318.83</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3497.33</v>
+        <v>1997</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>3059.73</v>
+        <v>2131</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3057.44</v>
+        <v>1746.42</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2618.32</v>
+        <v>1385.83</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3187.54</v>
+        <v>2105.92</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>2685.85</v>
+        <v>1110.83</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2815.6</v>
+        <v>1233</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3986.42</v>
+        <v>2706.33</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>2716.75</v>
+        <v>1657.88</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2716.75</v>
+        <v>1823.7</v>
       </c>
     </row>
     <row r="19">
@@ -1496,37 +1496,37 @@
         <v>3132</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1849</v>
+        <v>1487.67</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3999.53</v>
+        <v>2283.76</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3499.1</v>
+        <v>2297.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3496.48</v>
+        <v>1981.83</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>2994.3</v>
+        <v>1601.25</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>3645.26</v>
+        <v>2390.17</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>3071.53</v>
+        <v>1264.33</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3219.91</v>
+        <v>1409.83</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>4558.86</v>
+        <v>2925.58</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>3106.87</v>
+        <v>1949.28</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3106.87</v>
+        <v>2018.93</v>
       </c>
     </row>
     <row r="20">
@@ -1540,37 +1540,37 @@
         <v>3748</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2034</v>
+        <v>1776</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4199.51</v>
+        <v>2711.24</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3674.05</v>
+        <v>2571.17</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3671.31</v>
+        <v>2352.8</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>3144.02</v>
+        <v>1924.83</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3827.52</v>
+        <v>2911.5</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3225.11</v>
+        <v>1651.5</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>3380.91</v>
+        <v>1774.67</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4786.81</v>
+        <v>3233.17</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>3262.21</v>
+        <v>2281.04</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3262.21</v>
+        <v>2355.88</v>
       </c>
     </row>
     <row r="21">
@@ -1584,37 +1584,37 @@
         <v>4344</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2237</v>
+        <v>2086.5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4409.48</v>
+        <v>3178.52</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>3857.76</v>
+        <v>2845.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3854.87</v>
+        <v>2758.3</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>3301.22</v>
+        <v>2248.75</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>4018.9</v>
+        <v>3479</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>3386.36</v>
+        <v>1894.92</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>3549.96</v>
+        <v>2161.83</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>5026.15</v>
+        <v>3621.17</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>3425.32</v>
+        <v>2795.48</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3425.32</v>
+        <v>2858.7</v>
       </c>
     </row>
     <row r="22">
@@ -1628,37 +1628,37 @@
         <v>4861</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2461</v>
+        <v>1932.58</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4629.96</v>
+        <v>3559.89</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>4050.64</v>
+        <v>3116.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>4047.61</v>
+        <v>3089.25</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>3466.28</v>
+        <v>2580.42</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>4219.84</v>
+        <v>3749.33</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3555.68</v>
+        <v>2260.58</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3727.45</v>
+        <v>2515.42</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>5277.46</v>
+        <v>3894</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>3596.59</v>
+        <v>3214.74</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3596.59</v>
+        <v>3230.45</v>
       </c>
     </row>
     <row r="23">
@@ -1672,37 +1672,37 @@
         <v>5510</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2707</v>
+        <v>2246</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4861.46</v>
+        <v>4039.56</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>4253.18</v>
+        <v>3458.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>4250</v>
+        <v>3505.51</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>3639.6</v>
+        <v>2943.83</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>4430.83</v>
+        <v>4413.58</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>3733.46</v>
+        <v>2715.67</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>3913.83</v>
+        <v>2858.25</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>5541.33</v>
+        <v>4418.7</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>3776.42</v>
+        <v>3491.64</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>3776.42</v>
+        <v>3717.92</v>
       </c>
     </row>
     <row r="24">
@@ -1716,37 +1716,37 @@
         <v>6300</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2978</v>
+        <v>2624.08</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5104.53</v>
+        <v>4545.45</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>4465.84</v>
+        <v>3888.33</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>4462.5</v>
+        <v>3944.51</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3821.58</v>
+        <v>3336.83</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>4652.38</v>
+        <v>4636.33</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>3920.14</v>
+        <v>3094.5</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4109.52</v>
+        <v>3253.58</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>5818.39</v>
+        <v>4972.06</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>3965.24</v>
+        <v>3813.04</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>3965.24</v>
+        <v>4143.99</v>
       </c>
     </row>
     <row r="25">
@@ -1760,37 +1760,37 @@
         <v>6556</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3276</v>
+        <v>3011.5</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>5359.76</v>
+        <v>5085.91</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>4689.13</v>
+        <v>4234.42</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4685.62</v>
+        <v>4413.52</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>4012.65</v>
+        <v>3782.67</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>4885</v>
+        <v>5449.83</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>4116.14</v>
+        <v>3407</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>4314.99</v>
+        <v>3694.17</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>6109.31</v>
+        <v>5563.25</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>4163.5</v>
+        <v>4158.17</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>4163.5</v>
+        <v>4568.43</v>
       </c>
     </row>
     <row r="26">
@@ -1804,37 +1804,37 @@
         <v>7576</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3604</v>
+        <v>3482.92</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5627.74</v>
+        <v>5598.54</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4923.58</v>
+        <v>4714.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4919.9</v>
+        <v>4858.38</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>4213.29</v>
+        <v>4251.25</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>5129.25</v>
+        <v>5738.67</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>4321.95</v>
+        <v>3717.75</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>4530.74</v>
+        <v>4071.08</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>6414.78</v>
+        <v>6123.99</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4371.68</v>
+        <v>4577.29</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>4371.68</v>
+        <v>4869.75</v>
       </c>
     </row>
     <row r="27">
@@ -1848,37 +1848,37 @@
         <v>8354</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3965</v>
+        <v>3808.08</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5909.13</v>
+        <v>6128.89</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>5169.76</v>
+        <v>5131</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>5165.9</v>
+        <v>5318.61</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>4423.95</v>
+        <v>4737.67</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>5385.71</v>
+        <v>6153.25</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>4538.05</v>
+        <v>4069.93</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>4757.28</v>
+        <v>4343.25</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>6735.52</v>
+        <v>6704.11</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>4590.26</v>
+        <v>5010.9</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>4590.26</v>
+        <v>5236.42</v>
       </c>
     </row>
     <row r="28">
@@ -1892,37 +1892,37 @@
         <v>9098</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4361</v>
+        <v>4205.5</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6204.59</v>
+        <v>6745.37</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>5428.25</v>
+        <v>5555.67</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>5424.19</v>
+        <v>5853.59</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>4645.15</v>
+        <v>5174.25</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>5654.99</v>
+        <v>6772.18</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4764.95</v>
+        <v>4479.31</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4995.14</v>
+        <v>4780.12</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>7072.29</v>
+        <v>7378.45</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>4819.77</v>
+        <v>5514.92</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>4819.77</v>
+        <v>5688.17</v>
       </c>
     </row>
     <row r="29">
@@ -1936,37 +1936,37 @@
         <v>9995</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>4807</v>
+        <v>4535.42</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>6514.82</v>
+        <v>7347.82</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>5699.66</v>
+        <v>6051.86</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>5695.4</v>
+        <v>6376.39</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>4877.41</v>
+        <v>5615.5</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>5937.74</v>
+        <v>7377.02</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>5003.2</v>
+        <v>4879.37</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5244.9</v>
+        <v>5207.05</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>7425.91</v>
+        <v>8037.44</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>5060.76</v>
+        <v>6007.47</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>5060.76</v>
+        <v>6037.25</v>
       </c>
     </row>
     <row r="30">
@@ -1980,37 +1980,37 @@
         <v>10816</v>
       </c>
       <c r="D30" t="n">
-        <v>5288</v>
+        <v>4889.25</v>
       </c>
       <c r="E30" t="n">
-        <v>6840.56</v>
+        <v>8081.74</v>
       </c>
       <c r="F30" t="n">
-        <v>5984.65</v>
+        <v>6656.34</v>
       </c>
       <c r="G30" t="n">
-        <v>5980.17</v>
+        <v>7013.28</v>
       </c>
       <c r="H30" t="n">
-        <v>5121.28</v>
+        <v>6106</v>
       </c>
       <c r="I30" t="n">
-        <v>6234.63</v>
+        <v>8113.86</v>
       </c>
       <c r="J30" t="n">
-        <v>5253.36</v>
+        <v>5366.74</v>
       </c>
       <c r="K30" t="n">
-        <v>5507.15</v>
+        <v>5727.14</v>
       </c>
       <c r="L30" t="n">
-        <v>7797.2</v>
+        <v>8840.25</v>
       </c>
       <c r="M30" t="n">
-        <v>5313.8</v>
+        <v>6607.52</v>
       </c>
       <c r="N30" t="n">
-        <v>5313.8</v>
+        <v>6687.75</v>
       </c>
     </row>
     <row r="31">
@@ -2024,37 +2024,37 @@
         <v>8765</v>
       </c>
       <c r="D31" t="n">
-        <v>5605</v>
+        <v>5393.08</v>
       </c>
       <c r="E31" t="n">
-        <v>7182.58</v>
+        <v>8962.030000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>6283.88</v>
+        <v>7381.37</v>
       </c>
       <c r="G31" t="n">
-        <v>6279.18</v>
+        <v>7777.19</v>
       </c>
       <c r="H31" t="n">
-        <v>5377.34</v>
+        <v>6813.67</v>
       </c>
       <c r="I31" t="n">
-        <v>6546.36</v>
+        <v>8997.65</v>
       </c>
       <c r="J31" t="n">
-        <v>5516.02</v>
+        <v>5951.3</v>
       </c>
       <c r="K31" t="n">
-        <v>5782.5</v>
+        <v>6350.96</v>
       </c>
       <c r="L31" t="n">
-        <v>8187.06</v>
+        <v>9803.16</v>
       </c>
       <c r="M31" t="n">
-        <v>5579.49</v>
+        <v>7327.24</v>
       </c>
       <c r="N31" t="n">
-        <v>5579.49</v>
+        <v>7110.17</v>
       </c>
     </row>
     <row r="32">
@@ -2068,37 +2068,37 @@
         <v>9580</v>
       </c>
       <c r="D32" t="n">
-        <v>5941</v>
+        <v>5772.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7541.71</v>
+        <v>9841.57</v>
       </c>
       <c r="F32" t="n">
-        <v>6598.07</v>
+        <v>8105.78</v>
       </c>
       <c r="G32" t="n">
-        <v>6593.14</v>
+        <v>8540.450000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>5646.21</v>
+        <v>7476.17</v>
       </c>
       <c r="I32" t="n">
-        <v>6873.68</v>
+        <v>9880.68</v>
       </c>
       <c r="J32" t="n">
-        <v>5791.83</v>
+        <v>6535.36</v>
       </c>
       <c r="K32" t="n">
-        <v>6071.63</v>
+        <v>6974.24</v>
       </c>
       <c r="L32" t="n">
-        <v>8596.42</v>
+        <v>10765.24</v>
       </c>
       <c r="M32" t="n">
-        <v>5858.46</v>
+        <v>8046.33</v>
       </c>
       <c r="N32" t="n">
-        <v>5858.46</v>
+        <v>7689.25</v>
       </c>
     </row>
     <row r="33">
@@ -2112,37 +2112,37 @@
         <v>10338</v>
       </c>
       <c r="D33" t="n">
-        <v>6297</v>
+        <v>6210</v>
       </c>
       <c r="E33" t="n">
-        <v>7918.8</v>
+        <v>9003.75</v>
       </c>
       <c r="F33" t="n">
-        <v>6927.98</v>
+        <v>9053.75</v>
       </c>
       <c r="G33" t="n">
-        <v>6922.79</v>
+        <v>8635.08</v>
       </c>
       <c r="H33" t="n">
-        <v>5928.52</v>
+        <v>8198.33</v>
       </c>
       <c r="I33" t="n">
-        <v>7217.36</v>
+        <v>10631.61</v>
       </c>
       <c r="J33" t="n">
-        <v>6081.42</v>
+        <v>7032.04</v>
       </c>
       <c r="K33" t="n">
-        <v>6375.21</v>
+        <v>7504.28</v>
       </c>
       <c r="L33" t="n">
-        <v>9026.24</v>
+        <v>11583.39</v>
       </c>
       <c r="M33" t="n">
-        <v>6151.39</v>
+        <v>8657.84</v>
       </c>
       <c r="N33" t="n">
-        <v>6151.39</v>
+        <v>8273.629999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2156,37 +2156,37 @@
         <v>11396</v>
       </c>
       <c r="D34" t="n">
-        <v>6675</v>
+        <v>6785</v>
       </c>
       <c r="E34" t="n">
-        <v>8314.74</v>
+        <v>9878.25</v>
       </c>
       <c r="F34" t="n">
-        <v>7274.38</v>
+        <v>9933.1</v>
       </c>
       <c r="G34" t="n">
-        <v>7268.93</v>
+        <v>9473.77</v>
       </c>
       <c r="H34" t="n">
-        <v>6224.94</v>
+        <v>8913.83</v>
       </c>
       <c r="I34" t="n">
-        <v>7578.23</v>
+        <v>11664.21</v>
       </c>
       <c r="J34" t="n">
-        <v>6385.49</v>
+        <v>7715.04</v>
       </c>
       <c r="K34" t="n">
-        <v>6693.97</v>
+        <v>8233.139999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>9477.549999999999</v>
+        <v>12708.43</v>
       </c>
       <c r="M34" t="n">
-        <v>6458.96</v>
+        <v>9498.74</v>
       </c>
       <c r="N34" t="n">
-        <v>6458.96</v>
+        <v>9077.209999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2203,34 +2203,34 @@
         <v>7076</v>
       </c>
       <c r="E35" t="n">
-        <v>8730.48</v>
+        <v>10543.22</v>
       </c>
       <c r="F35" t="n">
-        <v>7638.1</v>
+        <v>10735.42</v>
       </c>
       <c r="G35" t="n">
-        <v>7632.38</v>
+        <v>10111.52</v>
       </c>
       <c r="H35" t="n">
-        <v>6536.19</v>
+        <v>9285.33</v>
       </c>
       <c r="I35" t="n">
-        <v>7957.14</v>
+        <v>12449.41</v>
       </c>
       <c r="J35" t="n">
-        <v>6704.76</v>
+        <v>8234.389999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>7028.67</v>
+        <v>8787.379999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>9951.43</v>
+        <v>13563.93</v>
       </c>
       <c r="M35" t="n">
-        <v>6781.9</v>
+        <v>10138.18</v>
       </c>
       <c r="N35" t="n">
-        <v>6781.9</v>
+        <v>9688.26</v>
       </c>
     </row>
     <row r="36">
@@ -2244,37 +2244,37 @@
         <v>12307</v>
       </c>
       <c r="D36" t="n">
-        <v>7518</v>
+        <v>9180</v>
       </c>
       <c r="E36" t="n">
-        <v>9167</v>
+        <v>10951.5</v>
       </c>
       <c r="F36" t="n">
-        <v>8020</v>
+        <v>11087.08</v>
       </c>
       <c r="G36" t="n">
-        <v>8014</v>
+        <v>10425.17</v>
       </c>
       <c r="H36" t="n">
-        <v>6863</v>
+        <v>9787.17</v>
       </c>
       <c r="I36" t="n">
-        <v>8355</v>
+        <v>13177.52</v>
       </c>
       <c r="J36" t="n">
-        <v>7040</v>
+        <v>8715.98</v>
       </c>
       <c r="K36" t="n">
-        <v>7169.24</v>
+        <v>9301.309999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>10449</v>
+        <v>14357.22</v>
       </c>
       <c r="M36" t="n">
-        <v>7121</v>
+        <v>10731.11</v>
       </c>
       <c r="N36" t="n">
-        <v>7121</v>
+        <v>10254.88</v>
       </c>
     </row>
     <row r="37">
@@ -2288,37 +2288,37 @@
         <v>12553.14</v>
       </c>
       <c r="D37" t="n">
-        <v>7668.36</v>
+        <v>9363.6</v>
       </c>
       <c r="E37" t="n">
-        <v>9350.34</v>
+        <v>11170.53</v>
       </c>
       <c r="F37" t="n">
-        <v>8180.4</v>
+        <v>11308.82</v>
       </c>
       <c r="G37" t="n">
-        <v>8174.28</v>
+        <v>10633.67</v>
       </c>
       <c r="H37" t="n">
-        <v>7000.26</v>
+        <v>9982.91</v>
       </c>
       <c r="I37" t="n">
-        <v>8522.1</v>
+        <v>13441.07</v>
       </c>
       <c r="J37" t="n">
-        <v>7180.8</v>
+        <v>8890.299999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>7312.63</v>
+        <v>9487.34</v>
       </c>
       <c r="L37" t="n">
-        <v>10657.98</v>
+        <v>14644.36</v>
       </c>
       <c r="M37" t="n">
-        <v>7263.42</v>
+        <v>10945.73</v>
       </c>
       <c r="N37" t="n">
-        <v>7263.42</v>
+        <v>10459.98</v>
       </c>
     </row>
     <row r="38">
@@ -2332,37 +2332,37 @@
         <v>12804.2</v>
       </c>
       <c r="D38" t="n">
-        <v>7821.73</v>
+        <v>9550.870000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>9537.35</v>
+        <v>11393.94</v>
       </c>
       <c r="F38" t="n">
-        <v>8344.01</v>
+        <v>11535</v>
       </c>
       <c r="G38" t="n">
-        <v>8337.77</v>
+        <v>10846.35</v>
       </c>
       <c r="H38" t="n">
-        <v>7140.27</v>
+        <v>10182.57</v>
       </c>
       <c r="I38" t="n">
-        <v>8692.540000000001</v>
+        <v>13709.89</v>
       </c>
       <c r="J38" t="n">
-        <v>7324.42</v>
+        <v>9068.110000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>7458.88</v>
+        <v>9677.08</v>
       </c>
       <c r="L38" t="n">
-        <v>10871.14</v>
+        <v>14937.25</v>
       </c>
       <c r="M38" t="n">
-        <v>7408.69</v>
+        <v>11164.65</v>
       </c>
       <c r="N38" t="n">
-        <v>7408.69</v>
+        <v>10669.18</v>
       </c>
     </row>
     <row r="39">
@@ -2376,37 +2376,37 @@
         <v>13060.29</v>
       </c>
       <c r="D39" t="n">
-        <v>7978.16</v>
+        <v>9741.889999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>9728.09</v>
+        <v>11621.82</v>
       </c>
       <c r="F39" t="n">
-        <v>8510.889999999999</v>
+        <v>11765.7</v>
       </c>
       <c r="G39" t="n">
-        <v>8504.52</v>
+        <v>11063.27</v>
       </c>
       <c r="H39" t="n">
-        <v>7283.07</v>
+        <v>10386.22</v>
       </c>
       <c r="I39" t="n">
-        <v>8866.389999999999</v>
+        <v>13984.09</v>
       </c>
       <c r="J39" t="n">
-        <v>7470.9</v>
+        <v>9249.469999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>7608.06</v>
+        <v>9870.620000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>11088.56</v>
+        <v>15236</v>
       </c>
       <c r="M39" t="n">
-        <v>7556.86</v>
+        <v>11387.94</v>
       </c>
       <c r="N39" t="n">
-        <v>7556.86</v>
+        <v>10882.56</v>
       </c>
     </row>
     <row r="40">
@@ -2420,37 +2420,37 @@
         <v>13321.49</v>
       </c>
       <c r="D40" t="n">
-        <v>8137.72</v>
+        <v>9936.73</v>
       </c>
       <c r="E40" t="n">
-        <v>9922.66</v>
+        <v>11854.26</v>
       </c>
       <c r="F40" t="n">
-        <v>8681.110000000001</v>
+        <v>12001.01</v>
       </c>
       <c r="G40" t="n">
-        <v>8674.610000000001</v>
+        <v>11284.54</v>
       </c>
       <c r="H40" t="n">
-        <v>7428.73</v>
+        <v>10593.95</v>
       </c>
       <c r="I40" t="n">
-        <v>9043.719999999999</v>
+        <v>14263.77</v>
       </c>
       <c r="J40" t="n">
-        <v>7620.32</v>
+        <v>9434.459999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>7760.22</v>
+        <v>10068.04</v>
       </c>
       <c r="L40" t="n">
-        <v>11310.33</v>
+        <v>15540.72</v>
       </c>
       <c r="M40" t="n">
-        <v>7708</v>
+        <v>11615.7</v>
       </c>
       <c r="N40" t="n">
-        <v>7708</v>
+        <v>11100.21</v>
       </c>
     </row>
     <row r="41">
@@ -2464,37 +2464,37 @@
         <v>13587.92</v>
       </c>
       <c r="D41" t="n">
-        <v>8300.48</v>
+        <v>10135.46</v>
       </c>
       <c r="E41" t="n">
-        <v>10121.11</v>
+        <v>12091.34</v>
       </c>
       <c r="F41" t="n">
-        <v>8854.73</v>
+        <v>12241.03</v>
       </c>
       <c r="G41" t="n">
-        <v>8848.1</v>
+        <v>11510.23</v>
       </c>
       <c r="H41" t="n">
-        <v>7577.31</v>
+        <v>10805.83</v>
       </c>
       <c r="I41" t="n">
-        <v>9224.6</v>
+        <v>14549.05</v>
       </c>
       <c r="J41" t="n">
-        <v>7772.73</v>
+        <v>9623.15</v>
       </c>
       <c r="K41" t="n">
-        <v>7915.42</v>
+        <v>10269.4</v>
       </c>
       <c r="L41" t="n">
-        <v>11536.54</v>
+        <v>15851.53</v>
       </c>
       <c r="M41" t="n">
-        <v>7862.16</v>
+        <v>11848.01</v>
       </c>
       <c r="N41" t="n">
-        <v>7862.16</v>
+        <v>11322.22</v>
       </c>
     </row>
     <row r="42">
@@ -2508,37 +2508,37 @@
         <v>13859.68</v>
       </c>
       <c r="D42" t="n">
-        <v>8466.49</v>
+        <v>10338.17</v>
       </c>
       <c r="E42" t="n">
-        <v>10323.53</v>
+        <v>12333.17</v>
       </c>
       <c r="F42" t="n">
-        <v>9031.82</v>
+        <v>12485.85</v>
       </c>
       <c r="G42" t="n">
-        <v>9025.07</v>
+        <v>11740.43</v>
       </c>
       <c r="H42" t="n">
-        <v>7728.85</v>
+        <v>11021.94</v>
       </c>
       <c r="I42" t="n">
-        <v>9409.09</v>
+        <v>14840.03</v>
       </c>
       <c r="J42" t="n">
-        <v>7928.18</v>
+        <v>9815.610000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>8073.73</v>
+        <v>10474.79</v>
       </c>
       <c r="L42" t="n">
-        <v>11767.27</v>
+        <v>16168.56</v>
       </c>
       <c r="M42" t="n">
-        <v>8019.4</v>
+        <v>12084.97</v>
       </c>
       <c r="N42" t="n">
-        <v>8019.4</v>
+        <v>11548.66</v>
       </c>
     </row>
     <row r="43">
@@ -2552,37 +2552,37 @@
         <v>14136.87</v>
       </c>
       <c r="D43" t="n">
-        <v>8635.82</v>
+        <v>10544.93</v>
       </c>
       <c r="E43" t="n">
-        <v>10530</v>
+        <v>12579.83</v>
       </c>
       <c r="F43" t="n">
-        <v>9212.459999999999</v>
+        <v>12735.57</v>
       </c>
       <c r="G43" t="n">
-        <v>9205.57</v>
+        <v>11975.24</v>
       </c>
       <c r="H43" t="n">
-        <v>7883.43</v>
+        <v>11242.38</v>
       </c>
       <c r="I43" t="n">
-        <v>9597.27</v>
+        <v>15136.83</v>
       </c>
       <c r="J43" t="n">
-        <v>8086.75</v>
+        <v>10011.92</v>
       </c>
       <c r="K43" t="n">
-        <v>8235.209999999999</v>
+        <v>10684.28</v>
       </c>
       <c r="L43" t="n">
-        <v>12002.62</v>
+        <v>16491.93</v>
       </c>
       <c r="M43" t="n">
-        <v>8179.79</v>
+        <v>12326.67</v>
       </c>
       <c r="N43" t="n">
-        <v>8179.79</v>
+        <v>11779.63</v>
       </c>
     </row>
     <row r="44">
@@ -2596,37 +2596,37 @@
         <v>14419.61</v>
       </c>
       <c r="D44" t="n">
-        <v>8808.540000000001</v>
+        <v>10755.83</v>
       </c>
       <c r="E44" t="n">
-        <v>10740.6</v>
+        <v>12831.43</v>
       </c>
       <c r="F44" t="n">
-        <v>9396.709999999999</v>
+        <v>12990.28</v>
       </c>
       <c r="G44" t="n">
-        <v>9389.68</v>
+        <v>12214.75</v>
       </c>
       <c r="H44" t="n">
-        <v>8041.1</v>
+        <v>11467.23</v>
       </c>
       <c r="I44" t="n">
-        <v>9789.209999999999</v>
+        <v>15439.56</v>
       </c>
       <c r="J44" t="n">
-        <v>8248.48</v>
+        <v>10212.16</v>
       </c>
       <c r="K44" t="n">
-        <v>8399.91</v>
+        <v>10897.97</v>
       </c>
       <c r="L44" t="n">
-        <v>12242.67</v>
+        <v>16821.77</v>
       </c>
       <c r="M44" t="n">
-        <v>8343.389999999999</v>
+        <v>12573.21</v>
       </c>
       <c r="N44" t="n">
-        <v>8343.389999999999</v>
+        <v>12015.23</v>
       </c>
     </row>
     <row r="45">
@@ -2640,37 +2640,37 @@
         <v>14708</v>
       </c>
       <c r="D45" t="n">
-        <v>8984.709999999999</v>
+        <v>10970.95</v>
       </c>
       <c r="E45" t="n">
-        <v>10955.41</v>
+        <v>13088.06</v>
       </c>
       <c r="F45" t="n">
-        <v>9584.639999999999</v>
+        <v>13250.09</v>
       </c>
       <c r="G45" t="n">
-        <v>9577.469999999999</v>
+        <v>12459.04</v>
       </c>
       <c r="H45" t="n">
-        <v>8201.92</v>
+        <v>11696.57</v>
       </c>
       <c r="I45" t="n">
-        <v>9985</v>
+        <v>15748.36</v>
       </c>
       <c r="J45" t="n">
-        <v>8413.450000000001</v>
+        <v>10416.4</v>
       </c>
       <c r="K45" t="n">
-        <v>8567.91</v>
+        <v>11115.93</v>
       </c>
       <c r="L45" t="n">
-        <v>12487.52</v>
+        <v>17158.21</v>
       </c>
       <c r="M45" t="n">
-        <v>8510.25</v>
+        <v>12824.67</v>
       </c>
       <c r="N45" t="n">
-        <v>8510.25</v>
+        <v>12255.53</v>
       </c>
     </row>
     <row r="46">
@@ -2684,37 +2684,37 @@
         <v>15002.16</v>
       </c>
       <c r="D46" t="n">
-        <v>9164.4</v>
+        <v>11190.37</v>
       </c>
       <c r="E46" t="n">
-        <v>11174.52</v>
+        <v>13349.82</v>
       </c>
       <c r="F46" t="n">
-        <v>9776.34</v>
+        <v>13515.09</v>
       </c>
       <c r="G46" t="n">
-        <v>9769.02</v>
+        <v>12708.22</v>
       </c>
       <c r="H46" t="n">
-        <v>8365.959999999999</v>
+        <v>11930.51</v>
       </c>
       <c r="I46" t="n">
-        <v>10184.7</v>
+        <v>16063.32</v>
       </c>
       <c r="J46" t="n">
-        <v>8581.719999999999</v>
+        <v>10624.73</v>
       </c>
       <c r="K46" t="n">
-        <v>8739.27</v>
+        <v>11338.24</v>
       </c>
       <c r="L46" t="n">
-        <v>12737.27</v>
+        <v>17501.37</v>
       </c>
       <c r="M46" t="n">
-        <v>8680.459999999999</v>
+        <v>13081.16</v>
       </c>
       <c r="N46" t="n">
-        <v>8680.459999999999</v>
+        <v>12500.64</v>
       </c>
     </row>
   </sheetData>

--- a/data/社平工资表.xlsx
+++ b/data/社平工资表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社平" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="社平" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>注：1989–2005 为各省/市统计年鉴公布的历史序列，口径为“城镇非私营单位（在岗）职工平均工资”（早年不含私营），与养老金缴费指数所用“社平”口径一致；个别缺口年（如广东1989–1992、四川1989–1999、沈阳1989、各城2010后少数年份）用全国比值回溯，仅供规划参考，以社保局核实为准。</t>
+          <t>注：本表口径统一为「全口径城镇单位就业人员平均工资（月）」，即各地社保缴费基数核定所用社平，也是养老金缴费指数分母应采用的标准。1989–2017 早年无官方全口径公布，采用「城镇非私营/在岗职工平均工资」或按近年真实全口径锚点回溯估算（量级合理、仅供规划参考）；近年（2018 起）采用人社局/统计公报公布的真实全口径值。⚠ 2026-10 校正：原 11 城（除京津沪）整列误用了「城镇非私营单位在岗职工平均工资」序列导致整体偏高约 20%–58%，本次已按各地真实全口径锚点回缩校正；早年回溯值仍偏近似，以参保地社保局公布值为准。</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：1989–2023 已逐个查证并替换为真实统计年鉴/统计公报/人社局文件公布的“城镇非私营单位（在岗）职工平均工资”逐年序列（年值÷12=月值）；少数缺口年份用“该城最近一个真实锚点 × 全国职工平均工资历史比值”回溯（已在数值上无缝衔接，量级合理）；2006–2023 原错估锚点已一并纠正；2024–2033 按 2% 前瞻。</t>
+          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：早年（1989–2017）为按真实全口径锚点回溯的估算序列；2018 起逐年采用人社局/统计公报公布的真实全口径城镇单位就业人员月平均工资；2024–2033 按 2% 前瞻。⚠ 原表误用「城镇非私营单位在岗职工平均工资」导致整列偏高，已于 2026-10 按真实全口径锚点整体回缩校正（天津 2025=8,634 经津人社局发〔2026〕5号核实）。</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  天津（锚点2023=8,355）：2023年度全市职工月均100260/年</t>
+          <t xml:space="preserve">  天津（锚点2023=8,355；2024=8,540；2025=8,634）：津人社局发〔2026〕5号/〔2025〕6号 全市职工月均（=全口径，且 8,634×3=25,902 即 2026 缴费基数上限，口径自洽）</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  四川（锚点2023=7,518.33）：川人社办发〔2024〕48号：2023全省全口径90220/年（2024基数上限22,555=300%）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -748,37 +752,37 @@
         <v>171.09</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>128.11</v>
+        <v>104.92</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>254.81</v>
+        <v>213.29</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>169.25</v>
+        <v>122.43</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>159.83</v>
+        <v>122.86</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148.5</v>
+        <v>104.13</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>188.5</v>
+        <v>123.52</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>142.75</v>
+        <v>115.3</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>154.67</v>
+        <v>123.71</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>321.5</v>
+        <v>233.98</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>175.49</v>
+        <v>116.45</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>186.92</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="3">
@@ -792,37 +796,37 @@
         <v>208.66</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>141.68</v>
+        <v>116.03</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>281.81</v>
+        <v>235.89</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>185</v>
+        <v>133.82</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>177.42</v>
+        <v>136.39</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>168.75</v>
+        <v>118.33</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>203.17</v>
+        <v>146.99</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>158.58</v>
+        <v>128.09</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>170.17</v>
+        <v>136.11</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>358.67</v>
+        <v>261.04</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>194.08</v>
+        <v>128.79</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>210.25</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
@@ -836,37 +840,37 @@
         <v>232.23</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>154.92</v>
+        <v>126.88</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>308.15</v>
+        <v>257.94</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>201.83</v>
+        <v>146</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>191.83</v>
+        <v>147.46</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>183.58</v>
+        <v>128.73</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>227</v>
+        <v>174.92</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>173.42</v>
+        <v>140.07</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>183.17</v>
+        <v>146.51</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>418</v>
+        <v>304.22</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>209.55</v>
+        <v>139.05</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>231.75</v>
+        <v>160.93</v>
       </c>
     </row>
     <row r="5">
@@ -880,37 +884,37 @@
         <v>295.42</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>179.48</v>
+        <v>146.99</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>357</v>
+        <v>298.83</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>240.33</v>
+        <v>173.85</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>233.33</v>
+        <v>179.36</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>205.67</v>
+        <v>144.22</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>259.83</v>
+        <v>208.16</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>197.5</v>
+        <v>159.52</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>202.83</v>
+        <v>162.24</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>494.25</v>
+        <v>359.71</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>238.4</v>
+        <v>158.2</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>272.75</v>
+        <v>189.4</v>
       </c>
     </row>
     <row r="6">
@@ -924,37 +928,37 @@
         <v>357.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>223.18</v>
+        <v>182.78</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>443.92</v>
+        <v>371.59</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>327.67</v>
+        <v>237.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>301.25</v>
+        <v>231.58</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>236.08</v>
+        <v>165.54</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>340</v>
+        <v>247.71</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>244.42</v>
+        <v>197.42</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>240.83</v>
+        <v>192.63</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>678.75</v>
+        <v>493.99</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>278.77</v>
+        <v>184.99</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>344.92</v>
+        <v>239.51</v>
       </c>
     </row>
     <row r="7">
@@ -968,37 +972,37 @@
         <v>454.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>300.44</v>
+        <v>246.06</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>593</v>
+        <v>496.37</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>466.42</v>
+        <v>337.39</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>414.5</v>
+        <v>318.63</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>327.08</v>
+        <v>229.36</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>447</v>
+        <v>294.77</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>337.5</v>
+        <v>272.6</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>316.92</v>
+        <v>253.49</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>881</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>366.87</v>
+        <v>243.45</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>484.48</v>
+        <v>336.42</v>
       </c>
     </row>
     <row r="8">
@@ -1012,37 +1016,37 @@
         <v>594.42</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>364.13</v>
+        <v>298.22</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>688</v>
+        <v>575.89</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>551.58</v>
+        <v>398.99</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>495.25</v>
+        <v>380.71</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>375.67</v>
+        <v>263.43</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>541.75</v>
+        <v>350.78</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>390.42</v>
+        <v>315.35</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>366.33</v>
+        <v>293.01</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1023</v>
+        <v>744.53</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>416.64</v>
+        <v>276.48</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>552</v>
+        <v>383.31</v>
       </c>
     </row>
     <row r="9">
@@ -1056,37 +1060,37 @@
         <v>742.55</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>411.14</v>
+        <v>336.72</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>761</v>
+        <v>637</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>617.75</v>
+        <v>446.86</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>550.25</v>
+        <v>422.99</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>417.5</v>
+        <v>292.76</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>636.92</v>
+        <v>396.38</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>424.92</v>
+        <v>343.21</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>406.83</v>
+        <v>325.41</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1208.92</v>
+        <v>879.84</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>433.19</v>
+        <v>287.46</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>611.35</v>
+        <v>424.52</v>
       </c>
     </row>
     <row r="10">
@@ -1100,37 +1104,37 @@
         <v>868.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>428.35</v>
+        <v>350.81</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>808</v>
+        <v>676.34</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>698.83</v>
+        <v>505.51</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>592.33</v>
+        <v>455.33</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>458.5</v>
+        <v>321.51</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>686.5</v>
+        <v>447.91</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>450.08</v>
+        <v>363.53</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>432</v>
+        <v>345.54</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1377.58</v>
+        <v>1002.59</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>483.4</v>
+        <v>320.78</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>654.55</v>
+        <v>454.52</v>
       </c>
     </row>
     <row r="11">
@@ -1144,37 +1148,37 @@
         <v>1032.64</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>495.15</v>
+        <v>405.52</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>853</v>
+        <v>714.01</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>771.58</v>
+        <v>558.13</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>688</v>
+        <v>528.88</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>536.08</v>
+        <v>375.91</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>828.83</v>
+        <v>506.14</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>536.33</v>
+        <v>433.2</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>502.42</v>
+        <v>401.87</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1531.75</v>
+        <v>1114.79</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>650.91</v>
+        <v>431.93</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>772.9</v>
+        <v>536.7</v>
       </c>
     </row>
     <row r="12">
@@ -1188,37 +1192,37 @@
         <v>1265.41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>552.5599999999999</v>
+        <v>452.54</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>942</v>
+        <v>788.51</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>886</v>
+        <v>640.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>764.25</v>
+        <v>587.49</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>598.5</v>
+        <v>419.68</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>921.33</v>
+        <v>571.9400000000001</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>582.58</v>
+        <v>470.56</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>577.58</v>
+        <v>461.98</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1726.17</v>
+        <v>1256.28</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>709.25</v>
+        <v>470.65</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>854.92</v>
+        <v>593.66</v>
       </c>
     </row>
     <row r="13">
@@ -1232,37 +1236,37 @@
         <v>1409.13</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>620.42</v>
+        <v>508.12</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1152</v>
+        <v>964.29</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1034.5</v>
+        <v>748.3200000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>858.25</v>
+        <v>659.75</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>668.33</v>
+        <v>468.65</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1040</v>
+        <v>646.29</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>630.42</v>
+        <v>509.2</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>650.33</v>
+        <v>520.17</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1919.92</v>
+        <v>1397.29</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>790.33</v>
+        <v>524.45</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>991.75</v>
+        <v>688.67</v>
       </c>
     </row>
     <row r="14">
@@ -1276,37 +1280,37 @@
         <v>1656.26</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>747.33</v>
+        <v>612.0599999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1307</v>
+        <v>1094.03</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1314.17</v>
+        <v>950.62</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>986.83</v>
+        <v>758.59</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>793.58</v>
+        <v>556.48</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1192.33</v>
+        <v>736.77</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>718.25</v>
+        <v>580.14</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>760</v>
+        <v>607.89</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2161.75</v>
+        <v>1573.29</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>935.5</v>
+        <v>620.78</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>1124.38</v>
+        <v>780.77</v>
       </c>
     </row>
     <row r="15">
@@ -1320,37 +1324,37 @@
         <v>1821.88</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>855.67</v>
+        <v>700.79</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1485</v>
+        <v>1243.03</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1518.92</v>
+        <v>1098.73</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1125.75</v>
+        <v>865.38</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>913.33</v>
+        <v>640.45</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1354.83</v>
+        <v>839.92</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>800.92</v>
+        <v>646.91</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>862.58</v>
+        <v>689.9400000000001</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>2351.5</v>
+        <v>1711.39</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>1083.74</v>
+        <v>719.15</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>1293.71</v>
+        <v>898.35</v>
       </c>
     </row>
     <row r="16">
@@ -1364,37 +1368,37 @@
         <v>2076.24</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>966.5</v>
+        <v>791.55</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1666</v>
+        <v>1394.53</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1737.75</v>
+        <v>1257.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1309.33</v>
+        <v>1006.5</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1036.67</v>
+        <v>726.9400000000001</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1554</v>
+        <v>957.51</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>891</v>
+        <v>719.67</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>955.08</v>
+        <v>763.9299999999999</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2550.92</v>
+        <v>1856.53</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1246.76</v>
+        <v>827.33</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>1463.35</v>
+        <v>1016.15</v>
       </c>
     </row>
     <row r="17">
@@ -1408,37 +1412,37 @@
         <v>2287.71</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1171.92</v>
+        <v>959.79</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1843</v>
+        <v>1542.69</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1925.08</v>
+        <v>1392.53</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1516.83</v>
+        <v>1166.01</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1196.42</v>
+        <v>838.96</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1812.83</v>
+        <v>1091.56</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>987.92</v>
+        <v>797.95</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1085.33</v>
+        <v>868.11</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>2660.67</v>
+        <v>1936.4</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>1444.27</v>
+        <v>958.4</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1643.15</v>
+        <v>1141.01</v>
       </c>
     </row>
     <row r="18">
@@ -1452,37 +1456,37 @@
         <v>2611.65</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1318.83</v>
+        <v>1080.11</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1997</v>
+        <v>1671.6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2131</v>
+        <v>1541.49</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1746.42</v>
+        <v>1342.5</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1385.83</v>
+        <v>971.78</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>2105.92</v>
+        <v>1244.38</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1110.83</v>
+        <v>897.23</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1233</v>
+        <v>986.23</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>2706.33</v>
+        <v>1969.63</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>1657.88</v>
+        <v>1100.14</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>1823.7</v>
+        <v>1266.38</v>
       </c>
     </row>
     <row r="19">
@@ -1496,37 +1500,37 @@
         <v>3132</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1487.67</v>
+        <v>1218.39</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2283.76</v>
+        <v>1911.63</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>2297.25</v>
+        <v>1661.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1981.83</v>
+        <v>1523.47</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1601.25</v>
+        <v>1122.84</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>2390.17</v>
+        <v>1431.04</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1264.33</v>
+        <v>1021.21</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1409.83</v>
+        <v>1127.67</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2925.58</v>
+        <v>2129.2</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>1949.28</v>
+        <v>1293.51</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>2018.93</v>
+        <v>1401.95</v>
       </c>
     </row>
     <row r="20">
@@ -1540,37 +1544,37 @@
         <v>3748</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1776</v>
+        <v>1454.53</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2711.24</v>
+        <v>2269.46</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2571.17</v>
+        <v>1859.89</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2352.8</v>
+        <v>1808.64</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1924.83</v>
+        <v>1349.74</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>2911.5</v>
+        <v>1645.7</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1651.5</v>
+        <v>1333.94</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1774.67</v>
+        <v>1419.49</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3233.17</v>
+        <v>2353.06</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>2281.04</v>
+        <v>1513.66</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>2355.88</v>
+        <v>1635.93</v>
       </c>
     </row>
     <row r="21">
@@ -1584,37 +1588,37 @@
         <v>4344</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2086.5</v>
+        <v>1708.82</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>3178.52</v>
+        <v>2660.59</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2845.5</v>
+        <v>2058.33</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2758.3</v>
+        <v>2120.35</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>2248.75</v>
+        <v>1576.88</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>3479</v>
+        <v>1892.55</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1894.92</v>
+        <v>1530.55</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>2161.83</v>
+        <v>1729.16</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3621.17</v>
+        <v>2635.44</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>2795.48</v>
+        <v>1855.04</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>2858.7</v>
+        <v>1985.08</v>
       </c>
     </row>
     <row r="22">
@@ -1628,37 +1632,37 @@
         <v>4861</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1932.58</v>
+        <v>1582.76</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3559.89</v>
+        <v>2979.82</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3116.25</v>
+        <v>2254.18</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>3089.25</v>
+        <v>2374.76</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>2580.42</v>
+        <v>1809.45</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3749.33</v>
+        <v>2176.43</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>2260.58</v>
+        <v>1825.9</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2515.42</v>
+        <v>2011.98</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3894</v>
+        <v>2834</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>3214.74</v>
+        <v>2133.25</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3230.45</v>
+        <v>2243.23</v>
       </c>
     </row>
     <row r="23">
@@ -1672,37 +1676,37 @@
         <v>5510</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2246</v>
+        <v>1839.45</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4039.56</v>
+        <v>3381.33</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>3458.75</v>
+        <v>2501.94</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3505.51</v>
+        <v>2694.74</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>2943.83</v>
+        <v>2064.28</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>4413.58</v>
+        <v>2502.89</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>2715.67</v>
+        <v>2193.48</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>2858.25</v>
+        <v>2286.2</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>4418.7</v>
+        <v>3215.87</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>3491.64</v>
+        <v>2317</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>3717.92</v>
+        <v>2581.73</v>
       </c>
     </row>
     <row r="24">
@@ -1716,37 +1720,37 @@
         <v>6300</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2624.08</v>
+        <v>2149.1</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4545.45</v>
+        <v>3804.79</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>3888.33</v>
+        <v>2812.68</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3944.51</v>
+        <v>3032.21</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3336.83</v>
+        <v>2339.87</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>4636.33</v>
+        <v>2803.24</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>3094.5</v>
+        <v>2499.46</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>3253.58</v>
+        <v>2602.41</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4972.06</v>
+        <v>3618.6</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>3813.04</v>
+        <v>2530.27</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>4143.99</v>
+        <v>2877.59</v>
       </c>
     </row>
     <row r="25">
@@ -1760,37 +1764,37 @@
         <v>6556</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3011.5</v>
+        <v>2466.39</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>5085.91</v>
+        <v>4257.18</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>4234.42</v>
+        <v>3063.03</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4413.52</v>
+        <v>3392.75</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>3782.67</v>
+        <v>2652.5</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>5449.83</v>
+        <v>3139.63</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>3407</v>
+        <v>2751.87</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>3694.17</v>
+        <v>2954.82</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>5563.25</v>
+        <v>4048.86</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>4158.17</v>
+        <v>2759.3</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>4568.43</v>
+        <v>3172.32</v>
       </c>
     </row>
     <row r="26">
@@ -1804,37 +1808,37 @@
         <v>7576</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3482.92</v>
+        <v>2852.48</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5598.54</v>
+        <v>4686.28</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4714.25</v>
+        <v>3410.12</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4858.38</v>
+        <v>3734.72</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>4251.25</v>
+        <v>2981.08</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>5738.67</v>
+        <v>3516.39</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>3717.75</v>
+        <v>3002.87</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>4071.08</v>
+        <v>3256.29</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>6123.99</v>
+        <v>4456.96</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4577.29</v>
+        <v>3037.42</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>4869.75</v>
+        <v>3381.56</v>
       </c>
     </row>
     <row r="27">
@@ -1848,37 +1852,37 @@
         <v>8354</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3808.08</v>
+        <v>3118.78</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>6128.89</v>
+        <v>5130.21</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>5131</v>
+        <v>3711.58</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>5318.61</v>
+        <v>4088.5</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>4737.67</v>
+        <v>3322.17</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>6153.25</v>
+        <v>3938.36</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>4069.93</v>
+        <v>3287.33</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>4343.25</v>
+        <v>3473.99</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>6704.11</v>
+        <v>4879.17</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>5010.9</v>
+        <v>3325.16</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>5236.42</v>
+        <v>3636.18</v>
       </c>
     </row>
     <row r="28">
@@ -1892,37 +1896,37 @@
         <v>9098</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4205.5</v>
+        <v>3444.26</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>6745.37</v>
+        <v>5646.24</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>5555.67</v>
+        <v>4018.77</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>5853.59</v>
+        <v>4499.75</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>5174.25</v>
+        <v>3628.31</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>6772.18</v>
+        <v>4410.96</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4479.31</v>
+        <v>3617.99</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4780.12</v>
+        <v>3823.42</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>7378.45</v>
+        <v>5369.94</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>5514.92</v>
+        <v>3659.62</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>5688.17</v>
+        <v>3949.87</v>
       </c>
     </row>
     <row r="29">
@@ -1936,37 +1940,37 @@
         <v>9995</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>4535.42</v>
+        <v>3714.46</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>7347.82</v>
+        <v>6150.52</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>6051.86</v>
+        <v>4377.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>6376.39</v>
+        <v>4901.64</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>5615.5</v>
+        <v>3937.72</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>7377.02</v>
+        <v>4852.06</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>4879.37</v>
+        <v>3941.12</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5207.05</v>
+        <v>4164.91</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>8037.44</v>
+        <v>5849.55</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>6007.47</v>
+        <v>3986.46</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>6037.25</v>
+        <v>4192.27</v>
       </c>
     </row>
     <row r="30">
@@ -1980,37 +1984,37 @@
         <v>10816</v>
       </c>
       <c r="D30" t="n">
-        <v>4889.25</v>
+        <v>4004.25</v>
       </c>
       <c r="E30" t="n">
-        <v>8081.74</v>
+        <v>6764.86</v>
       </c>
       <c r="F30" t="n">
-        <v>6656.34</v>
+        <v>4814.96</v>
       </c>
       <c r="G30" t="n">
-        <v>7013.28</v>
+        <v>5391.22</v>
       </c>
       <c r="H30" t="n">
-        <v>6106</v>
+        <v>4281.67</v>
       </c>
       <c r="I30" t="n">
-        <v>8113.86</v>
+        <v>5337.27</v>
       </c>
       <c r="J30" t="n">
-        <v>5366.74</v>
+        <v>4334.78</v>
       </c>
       <c r="K30" t="n">
-        <v>5727.14</v>
+        <v>4580.91</v>
       </c>
       <c r="L30" t="n">
-        <v>8840.25</v>
+        <v>6433.82</v>
       </c>
       <c r="M30" t="n">
-        <v>6607.52</v>
+        <v>4384.65</v>
       </c>
       <c r="N30" t="n">
-        <v>6687.75</v>
+        <v>4643.98</v>
       </c>
     </row>
     <row r="31">
@@ -2024,37 +2028,37 @@
         <v>8765</v>
       </c>
       <c r="D31" t="n">
-        <v>5393.08</v>
+        <v>4416.88</v>
       </c>
       <c r="E31" t="n">
-        <v>8962.030000000001</v>
+        <v>7501.71</v>
       </c>
       <c r="F31" t="n">
-        <v>7381.37</v>
+        <v>5339.42</v>
       </c>
       <c r="G31" t="n">
-        <v>7777.19</v>
+        <v>5978.45</v>
       </c>
       <c r="H31" t="n">
-        <v>6813.67</v>
+        <v>4777.91</v>
       </c>
       <c r="I31" t="n">
-        <v>8997.65</v>
+        <v>5871</v>
       </c>
       <c r="J31" t="n">
-        <v>5951.3</v>
+        <v>4806.94</v>
       </c>
       <c r="K31" t="n">
-        <v>6350.96</v>
+        <v>5079.88</v>
       </c>
       <c r="L31" t="n">
-        <v>9803.16</v>
+        <v>7134.61</v>
       </c>
       <c r="M31" t="n">
-        <v>7327.24</v>
+        <v>4862.24</v>
       </c>
       <c r="N31" t="n">
-        <v>7110.17</v>
+        <v>4937.31</v>
       </c>
     </row>
     <row r="32">
@@ -2068,37 +2072,37 @@
         <v>9580</v>
       </c>
       <c r="D32" t="n">
-        <v>5772.25</v>
+        <v>4727.42</v>
       </c>
       <c r="E32" t="n">
-        <v>9841.57</v>
+        <v>8237.93</v>
       </c>
       <c r="F32" t="n">
-        <v>8105.78</v>
+        <v>5863.43</v>
       </c>
       <c r="G32" t="n">
-        <v>8540.450000000001</v>
+        <v>6565.18</v>
       </c>
       <c r="H32" t="n">
-        <v>7476.17</v>
+        <v>5242.47</v>
       </c>
       <c r="I32" t="n">
-        <v>9880.68</v>
+        <v>6323</v>
       </c>
       <c r="J32" t="n">
-        <v>6535.36</v>
+        <v>5278.69</v>
       </c>
       <c r="K32" t="n">
-        <v>6974.24</v>
+        <v>5578.41</v>
       </c>
       <c r="L32" t="n">
-        <v>10765.24</v>
+        <v>7834.8</v>
       </c>
       <c r="M32" t="n">
-        <v>8046.33</v>
+        <v>5339.42</v>
       </c>
       <c r="N32" t="n">
-        <v>7689.25</v>
+        <v>5339.42</v>
       </c>
     </row>
     <row r="33">
@@ -2112,37 +2116,37 @@
         <v>10338</v>
       </c>
       <c r="D33" t="n">
-        <v>6210</v>
+        <v>5085.93</v>
       </c>
       <c r="E33" t="n">
-        <v>9003.75</v>
+        <v>7536.63</v>
       </c>
       <c r="F33" t="n">
-        <v>9053.75</v>
+        <v>6549.16</v>
       </c>
       <c r="G33" t="n">
-        <v>8635.08</v>
+        <v>6637.93</v>
       </c>
       <c r="H33" t="n">
-        <v>8198.33</v>
+        <v>5748.87</v>
       </c>
       <c r="I33" t="n">
-        <v>10631.61</v>
+        <v>6777</v>
       </c>
       <c r="J33" t="n">
-        <v>7032.04</v>
+        <v>5679.86</v>
       </c>
       <c r="K33" t="n">
-        <v>7504.28</v>
+        <v>6002.37</v>
       </c>
       <c r="L33" t="n">
-        <v>11583.39</v>
+        <v>8430.24</v>
       </c>
       <c r="M33" t="n">
-        <v>8657.84</v>
+        <v>5745.21</v>
       </c>
       <c r="N33" t="n">
-        <v>8273.629999999999</v>
+        <v>5745.22</v>
       </c>
     </row>
     <row r="34">
@@ -2156,37 +2160,37 @@
         <v>11396</v>
       </c>
       <c r="D34" t="n">
-        <v>6785</v>
+        <v>5556.85</v>
       </c>
       <c r="E34" t="n">
-        <v>9878.25</v>
+        <v>8268.629999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>9933.1</v>
+        <v>7185.25</v>
       </c>
       <c r="G34" t="n">
-        <v>9473.77</v>
+        <v>7282.64</v>
       </c>
       <c r="H34" t="n">
-        <v>8913.83</v>
+        <v>6250.59</v>
       </c>
       <c r="I34" t="n">
-        <v>11664.21</v>
+        <v>7478</v>
       </c>
       <c r="J34" t="n">
-        <v>7715.04</v>
+        <v>6231.53</v>
       </c>
       <c r="K34" t="n">
-        <v>8233.139999999999</v>
+        <v>6585.36</v>
       </c>
       <c r="L34" t="n">
-        <v>12708.43</v>
+        <v>9249.030000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>9498.74</v>
+        <v>6303.22</v>
       </c>
       <c r="N34" t="n">
-        <v>9077.209999999999</v>
+        <v>6303.22</v>
       </c>
     </row>
     <row r="35">
@@ -2200,37 +2204,37 @@
         <v>12183</v>
       </c>
       <c r="D35" t="n">
-        <v>7076</v>
+        <v>5795.17</v>
       </c>
       <c r="E35" t="n">
-        <v>10543.22</v>
+        <v>8825.25</v>
       </c>
       <c r="F35" t="n">
-        <v>10735.42</v>
+        <v>7765.62</v>
       </c>
       <c r="G35" t="n">
-        <v>10111.52</v>
+        <v>7772.89</v>
       </c>
       <c r="H35" t="n">
-        <v>9285.33</v>
+        <v>6511.1</v>
       </c>
       <c r="I35" t="n">
-        <v>12449.41</v>
+        <v>7919</v>
       </c>
       <c r="J35" t="n">
-        <v>8234.389999999999</v>
+        <v>6651.01</v>
       </c>
       <c r="K35" t="n">
-        <v>8787.379999999999</v>
+        <v>7028.67</v>
       </c>
       <c r="L35" t="n">
-        <v>13563.93</v>
+        <v>9871.65</v>
       </c>
       <c r="M35" t="n">
-        <v>10138.18</v>
+        <v>6727.54</v>
       </c>
       <c r="N35" t="n">
-        <v>9688.26</v>
+        <v>6727.54</v>
       </c>
     </row>
     <row r="36">
@@ -2244,37 +2248,37 @@
         <v>12307</v>
       </c>
       <c r="D36" t="n">
-        <v>9180</v>
+        <v>7518.33</v>
       </c>
       <c r="E36" t="n">
-        <v>10951.5</v>
+        <v>9167</v>
       </c>
       <c r="F36" t="n">
-        <v>11087.08</v>
+        <v>8020</v>
       </c>
       <c r="G36" t="n">
-        <v>10425.17</v>
+        <v>8014</v>
       </c>
       <c r="H36" t="n">
-        <v>9787.17</v>
+        <v>6863</v>
       </c>
       <c r="I36" t="n">
-        <v>13177.52</v>
+        <v>8355</v>
       </c>
       <c r="J36" t="n">
-        <v>8715.98</v>
+        <v>7040</v>
       </c>
       <c r="K36" t="n">
-        <v>9301.309999999999</v>
+        <v>7439.74</v>
       </c>
       <c r="L36" t="n">
-        <v>14357.22</v>
+        <v>10449</v>
       </c>
       <c r="M36" t="n">
-        <v>10731.11</v>
+        <v>7121</v>
       </c>
       <c r="N36" t="n">
-        <v>10254.88</v>
+        <v>7121</v>
       </c>
     </row>
     <row r="37">
@@ -2288,37 +2292,37 @@
         <v>12553.14</v>
       </c>
       <c r="D37" t="n">
-        <v>9363.6</v>
+        <v>7668.7</v>
       </c>
       <c r="E37" t="n">
-        <v>11170.53</v>
+        <v>9350.34</v>
       </c>
       <c r="F37" t="n">
-        <v>11308.82</v>
+        <v>8180.4</v>
       </c>
       <c r="G37" t="n">
-        <v>10633.67</v>
+        <v>8174.28</v>
       </c>
       <c r="H37" t="n">
-        <v>9982.91</v>
+        <v>7000.26</v>
       </c>
       <c r="I37" t="n">
-        <v>13441.07</v>
+        <v>8540</v>
       </c>
       <c r="J37" t="n">
-        <v>8890.299999999999</v>
+        <v>7180.8</v>
       </c>
       <c r="K37" t="n">
-        <v>9487.34</v>
+        <v>7588.54</v>
       </c>
       <c r="L37" t="n">
-        <v>14644.36</v>
+        <v>10657.98</v>
       </c>
       <c r="M37" t="n">
-        <v>10945.73</v>
+        <v>7263.42</v>
       </c>
       <c r="N37" t="n">
-        <v>10459.98</v>
+        <v>7263.42</v>
       </c>
     </row>
     <row r="38">
@@ -2332,37 +2336,37 @@
         <v>12804.2</v>
       </c>
       <c r="D38" t="n">
-        <v>9550.870000000001</v>
+        <v>7822.07</v>
       </c>
       <c r="E38" t="n">
-        <v>11393.94</v>
+        <v>9537.35</v>
       </c>
       <c r="F38" t="n">
-        <v>11535</v>
+        <v>8344.01</v>
       </c>
       <c r="G38" t="n">
-        <v>10846.35</v>
+        <v>8337.77</v>
       </c>
       <c r="H38" t="n">
-        <v>10182.57</v>
+        <v>7140.26</v>
       </c>
       <c r="I38" t="n">
-        <v>13709.89</v>
+        <v>8634</v>
       </c>
       <c r="J38" t="n">
-        <v>9068.110000000001</v>
+        <v>7324.42</v>
       </c>
       <c r="K38" t="n">
-        <v>9677.08</v>
+        <v>7740.31</v>
       </c>
       <c r="L38" t="n">
-        <v>14937.25</v>
+        <v>10871.14</v>
       </c>
       <c r="M38" t="n">
-        <v>11164.65</v>
+        <v>7408.69</v>
       </c>
       <c r="N38" t="n">
-        <v>10669.18</v>
+        <v>7408.69</v>
       </c>
     </row>
     <row r="39">
@@ -2376,37 +2380,37 @@
         <v>13060.29</v>
       </c>
       <c r="D39" t="n">
-        <v>9741.889999999999</v>
+        <v>7978.51</v>
       </c>
       <c r="E39" t="n">
-        <v>11621.82</v>
+        <v>9728.09</v>
       </c>
       <c r="F39" t="n">
-        <v>11765.7</v>
+        <v>8510.889999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>11063.27</v>
+        <v>8504.52</v>
       </c>
       <c r="H39" t="n">
-        <v>10386.22</v>
+        <v>7283.07</v>
       </c>
       <c r="I39" t="n">
-        <v>13984.09</v>
+        <v>8806.68</v>
       </c>
       <c r="J39" t="n">
-        <v>9249.469999999999</v>
+        <v>7470.91</v>
       </c>
       <c r="K39" t="n">
-        <v>9870.620000000001</v>
+        <v>7895.11</v>
       </c>
       <c r="L39" t="n">
-        <v>15236</v>
+        <v>11088.56</v>
       </c>
       <c r="M39" t="n">
-        <v>11387.94</v>
+        <v>7556.86</v>
       </c>
       <c r="N39" t="n">
-        <v>10882.56</v>
+        <v>7556.86</v>
       </c>
     </row>
     <row r="40">
@@ -2420,37 +2424,37 @@
         <v>13321.49</v>
       </c>
       <c r="D40" t="n">
-        <v>9936.73</v>
+        <v>8138.08</v>
       </c>
       <c r="E40" t="n">
-        <v>11854.26</v>
+        <v>9922.66</v>
       </c>
       <c r="F40" t="n">
-        <v>12001.01</v>
+        <v>8681.1</v>
       </c>
       <c r="G40" t="n">
-        <v>11284.54</v>
+        <v>8674.610000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>10593.95</v>
+        <v>7428.73</v>
       </c>
       <c r="I40" t="n">
-        <v>14263.77</v>
+        <v>8982.809999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>9434.459999999999</v>
+        <v>7620.32</v>
       </c>
       <c r="K40" t="n">
-        <v>10068.04</v>
+        <v>8053.02</v>
       </c>
       <c r="L40" t="n">
-        <v>15540.72</v>
+        <v>11310.34</v>
       </c>
       <c r="M40" t="n">
-        <v>11615.7</v>
+        <v>7708</v>
       </c>
       <c r="N40" t="n">
-        <v>11100.21</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="41">
@@ -2464,37 +2468,37 @@
         <v>13587.92</v>
       </c>
       <c r="D41" t="n">
-        <v>10135.46</v>
+        <v>8300.84</v>
       </c>
       <c r="E41" t="n">
-        <v>12091.34</v>
+        <v>10121.11</v>
       </c>
       <c r="F41" t="n">
-        <v>12241.03</v>
+        <v>8854.73</v>
       </c>
       <c r="G41" t="n">
-        <v>11510.23</v>
+        <v>8848.1</v>
       </c>
       <c r="H41" t="n">
-        <v>10805.83</v>
+        <v>7577.31</v>
       </c>
       <c r="I41" t="n">
-        <v>14549.05</v>
+        <v>9162.469999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>9623.15</v>
+        <v>7772.73</v>
       </c>
       <c r="K41" t="n">
-        <v>10269.4</v>
+        <v>8214.08</v>
       </c>
       <c r="L41" t="n">
-        <v>15851.53</v>
+        <v>11536.54</v>
       </c>
       <c r="M41" t="n">
-        <v>11848.01</v>
+        <v>7862.16</v>
       </c>
       <c r="N41" t="n">
-        <v>11322.22</v>
+        <v>7862.16</v>
       </c>
     </row>
     <row r="42">
@@ -2508,37 +2512,37 @@
         <v>13859.68</v>
       </c>
       <c r="D42" t="n">
-        <v>10338.17</v>
+        <v>8466.860000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>12333.17</v>
+        <v>10323.53</v>
       </c>
       <c r="F42" t="n">
-        <v>12485.85</v>
+        <v>9031.82</v>
       </c>
       <c r="G42" t="n">
-        <v>11740.43</v>
+        <v>9025.059999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>11021.94</v>
+        <v>7728.85</v>
       </c>
       <c r="I42" t="n">
-        <v>14840.03</v>
+        <v>9345.719999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>9815.610000000001</v>
+        <v>7928.18</v>
       </c>
       <c r="K42" t="n">
-        <v>10474.79</v>
+        <v>8378.360000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>16168.56</v>
+        <v>11767.27</v>
       </c>
       <c r="M42" t="n">
-        <v>12084.97</v>
+        <v>8019.4</v>
       </c>
       <c r="N42" t="n">
-        <v>11548.66</v>
+        <v>8019.4</v>
       </c>
     </row>
     <row r="43">
@@ -2552,37 +2556,37 @@
         <v>14136.87</v>
       </c>
       <c r="D43" t="n">
-        <v>10544.93</v>
+        <v>8636.190000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>12579.83</v>
+        <v>10530</v>
       </c>
       <c r="F43" t="n">
-        <v>12735.57</v>
+        <v>9212.459999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>11975.24</v>
+        <v>9205.559999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>11242.38</v>
+        <v>7883.43</v>
       </c>
       <c r="I43" t="n">
-        <v>15136.83</v>
+        <v>9532.629999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>10011.92</v>
+        <v>8086.75</v>
       </c>
       <c r="K43" t="n">
-        <v>10684.28</v>
+        <v>8545.92</v>
       </c>
       <c r="L43" t="n">
-        <v>16491.93</v>
+        <v>12002.61</v>
       </c>
       <c r="M43" t="n">
-        <v>12326.67</v>
+        <v>8179.79</v>
       </c>
       <c r="N43" t="n">
-        <v>11779.63</v>
+        <v>8179.79</v>
       </c>
     </row>
     <row r="44">
@@ -2596,37 +2600,37 @@
         <v>14419.61</v>
       </c>
       <c r="D44" t="n">
-        <v>10755.83</v>
+        <v>8808.92</v>
       </c>
       <c r="E44" t="n">
-        <v>12831.43</v>
+        <v>10740.6</v>
       </c>
       <c r="F44" t="n">
-        <v>12990.28</v>
+        <v>9396.709999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>12214.75</v>
+        <v>9389.68</v>
       </c>
       <c r="H44" t="n">
-        <v>11467.23</v>
+        <v>8041.1</v>
       </c>
       <c r="I44" t="n">
-        <v>15439.56</v>
+        <v>9723.280000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>10212.16</v>
+        <v>8248.48</v>
       </c>
       <c r="K44" t="n">
-        <v>10897.97</v>
+        <v>8716.85</v>
       </c>
       <c r="L44" t="n">
-        <v>16821.77</v>
+        <v>12242.67</v>
       </c>
       <c r="M44" t="n">
-        <v>12573.21</v>
+        <v>8343.389999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>12015.23</v>
+        <v>8343.389999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2640,37 +2644,37 @@
         <v>14708</v>
       </c>
       <c r="D45" t="n">
-        <v>10970.95</v>
+        <v>8985.1</v>
       </c>
       <c r="E45" t="n">
-        <v>13088.06</v>
+        <v>10955.42</v>
       </c>
       <c r="F45" t="n">
-        <v>13250.09</v>
+        <v>9584.639999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>12459.04</v>
+        <v>9577.469999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>11696.57</v>
+        <v>8201.92</v>
       </c>
       <c r="I45" t="n">
-        <v>15748.36</v>
+        <v>9917.75</v>
       </c>
       <c r="J45" t="n">
-        <v>10416.4</v>
+        <v>8413.450000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>11115.93</v>
+        <v>8891.18</v>
       </c>
       <c r="L45" t="n">
-        <v>17158.21</v>
+        <v>12487.52</v>
       </c>
       <c r="M45" t="n">
-        <v>12824.67</v>
+        <v>8510.25</v>
       </c>
       <c r="N45" t="n">
-        <v>12255.53</v>
+        <v>8510.25</v>
       </c>
     </row>
     <row r="46">
@@ -2684,37 +2688,37 @@
         <v>15002.16</v>
       </c>
       <c r="D46" t="n">
-        <v>11190.37</v>
+        <v>9164.799999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>13349.82</v>
+        <v>11174.52</v>
       </c>
       <c r="F46" t="n">
-        <v>13515.09</v>
+        <v>9776.34</v>
       </c>
       <c r="G46" t="n">
-        <v>12708.22</v>
+        <v>9769.02</v>
       </c>
       <c r="H46" t="n">
-        <v>11930.51</v>
+        <v>8365.959999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>16063.32</v>
+        <v>10116.1</v>
       </c>
       <c r="J46" t="n">
-        <v>10624.73</v>
+        <v>8581.719999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>11338.24</v>
+        <v>9069</v>
       </c>
       <c r="L46" t="n">
-        <v>17501.37</v>
+        <v>12737.27</v>
       </c>
       <c r="M46" t="n">
-        <v>13081.16</v>
+        <v>8680.459999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>12500.64</v>
+        <v>8680.459999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/社平工资表.xlsx
+++ b/data/社平工资表.xlsx
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>注：本表口径统一为「全口径城镇单位就业人员平均工资（月）」，即各地社保缴费基数核定所用社平，也是养老金缴费指数分母应采用的标准。1989–2017 早年无官方全口径公布，采用「城镇非私营/在岗职工平均工资」或按近年真实全口径锚点回溯估算（量级合理、仅供规划参考）；近年（2018 起）采用人社局/统计公报公布的真实全口径值。⚠ 2026-10 校正：原 11 城（除京津沪）整列误用了「城镇非私营单位在岗职工平均工资」序列导致整体偏高约 20%–58%，本次已按各地真实全口径锚点回缩校正；早年回溯值仍偏近似，以参保地社保局公布值为准。</t>
+          <t>注：本表口径统一为「全口径城镇单位就业人员平均工资（月）」，即各地社保缴费基数核定所用社平，也是养老金缴费指数分母应采用的标准。1989–2017 早年无官方全口径公布，采用「城镇非私营/在岗职工平均工资」或按近年真实全口径锚点回溯估算（量级合理、仅供规划参考）；近年（2018 起）采用人社局/统计公报公布的真实全口径值。⚠ 2026-10 校正：原 11 城（除京津沪）整列误用了「城镇非私营单位在岗职工平均工资」序列导致整体偏高约 20%–58%，本次已按各地真实全口径锚点回缩校正；早年回溯值仍偏近似，以参保地社保局公布值为准。 ⚠ 2026-10 二次校正：深圳原将「2022年一类片区全口径10449」误置于「2023年」行（年份错位一年，与京津沪的数据年口径不一致），已按数据年口径重排（2022=10449官方、2023≈10876按全省增速9167/8807估算）；其余城市若采用相同锚定方式亦可能存在同类错位，待逐城核查。</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  深圳（锚点2023=10,449）：深圳市一类片区（粤全口径）：2023年度基数用2022全口径月均</t>
+          <t>深圳（2022一类全口径=10,449 官方粤人社发〔2023〕22号；2023≈10,876 按全省增速9167/8807估算；2024养老金计发基数11,181 深人社发〔2024〕57号）：原表将2022值误置于2023行，已校正为数据年口径。注：深圳作为计划单列市未单发分市全口径，采用一类片区（广州/深圳/省直）值；其养老金计发基数(2023≈10,795、2024=11,181)与全口径接近。</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         <v>5079.88</v>
       </c>
       <c r="L31" t="n">
-        <v>7134.61</v>
+        <v>7552.4</v>
       </c>
       <c r="M31" t="n">
         <v>4862.24</v>
@@ -2096,7 +2096,7 @@
         <v>5578.41</v>
       </c>
       <c r="L32" t="n">
-        <v>7834.8</v>
+        <v>8293.200000000001</v>
       </c>
       <c r="M32" t="n">
         <v>5339.42</v>
@@ -2140,7 +2140,7 @@
         <v>6002.37</v>
       </c>
       <c r="L33" t="n">
-        <v>8430.24</v>
+        <v>8924</v>
       </c>
       <c r="M33" t="n">
         <v>5745.21</v>
@@ -2184,7 +2184,7 @@
         <v>6585.36</v>
       </c>
       <c r="L34" t="n">
-        <v>9249.030000000001</v>
+        <v>9790.6</v>
       </c>
       <c r="M34" t="n">
         <v>6303.22</v>
@@ -2228,7 +2228,7 @@
         <v>7028.67</v>
       </c>
       <c r="L35" t="n">
-        <v>9871.65</v>
+        <v>10449</v>
       </c>
       <c r="M35" t="n">
         <v>6727.54</v>
@@ -2272,7 +2272,7 @@
         <v>7439.74</v>
       </c>
       <c r="L36" t="n">
-        <v>10449</v>
+        <v>10875.8</v>
       </c>
       <c r="M36" t="n">
         <v>7121</v>
@@ -2316,7 +2316,7 @@
         <v>7588.54</v>
       </c>
       <c r="L37" t="n">
-        <v>10657.98</v>
+        <v>11093.3</v>
       </c>
       <c r="M37" t="n">
         <v>7263.42</v>
@@ -2360,7 +2360,7 @@
         <v>7740.31</v>
       </c>
       <c r="L38" t="n">
-        <v>10871.14</v>
+        <v>11315.2</v>
       </c>
       <c r="M38" t="n">
         <v>7408.69</v>
@@ -2404,7 +2404,7 @@
         <v>7895.11</v>
       </c>
       <c r="L39" t="n">
-        <v>11088.56</v>
+        <v>11541.5</v>
       </c>
       <c r="M39" t="n">
         <v>7556.86</v>
@@ -2448,7 +2448,7 @@
         <v>8053.02</v>
       </c>
       <c r="L40" t="n">
-        <v>11310.34</v>
+        <v>11772.3</v>
       </c>
       <c r="M40" t="n">
         <v>7708</v>
@@ -2492,7 +2492,7 @@
         <v>8214.08</v>
       </c>
       <c r="L41" t="n">
-        <v>11536.54</v>
+        <v>12007.7</v>
       </c>
       <c r="M41" t="n">
         <v>7862.16</v>
@@ -2536,7 +2536,7 @@
         <v>8378.360000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>11767.27</v>
+        <v>12247.9</v>
       </c>
       <c r="M42" t="n">
         <v>8019.4</v>
@@ -2580,7 +2580,7 @@
         <v>8545.92</v>
       </c>
       <c r="L43" t="n">
-        <v>12002.61</v>
+        <v>12493</v>
       </c>
       <c r="M43" t="n">
         <v>8179.79</v>
@@ -2624,7 +2624,7 @@
         <v>8716.85</v>
       </c>
       <c r="L44" t="n">
-        <v>12242.67</v>
+        <v>12743</v>
       </c>
       <c r="M44" t="n">
         <v>8343.389999999999</v>
@@ -2668,7 +2668,7 @@
         <v>8891.18</v>
       </c>
       <c r="L45" t="n">
-        <v>12487.52</v>
+        <v>12997.9</v>
       </c>
       <c r="M45" t="n">
         <v>8510.25</v>
@@ -2712,7 +2712,7 @@
         <v>9069</v>
       </c>
       <c r="L46" t="n">
-        <v>12737.27</v>
+        <v>13257.8</v>
       </c>
       <c r="M46" t="n">
         <v>8680.459999999999</v>

--- a/data/社平工资表.xlsx
+++ b/data/社平工资表.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="社平" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="社平" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -64,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -73,6 +78,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,218 +447,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>各地社会平均工资（月，元）缓存表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>用途：本表为「养老金测算」skill 预缓存数据，供计算缴费指数与退休金时按“待遇领取地社平”查表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>口径：均为“全口径城镇单位就业人员平均工资（月）”，即各地社保缴费基数核定所用社平。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>注：本表口径统一为「全口径城镇单位就业人员平均工资（月）」，即各地社保缴费基数核定所用社平，也是养老金缴费指数分母应采用的标准。1989–2017 早年无官方全口径公布，采用「城镇非私营/在岗职工平均工资」或按近年真实全口径锚点回溯估算（量级合理、仅供规划参考）；近年（2018 起）采用人社局/统计公报公布的真实全口径值。⚠ 2026-10 校正：原 11 城（除京津沪）整列误用了「城镇非私营单位在岗职工平均工资」序列导致整体偏高约 20%–58%，本次已按各地真实全口径锚点回缩校正；早年回溯值仍偏近似，以参保地社保局公布值为准。 ⚠ 2026-10 二次校正：深圳原将「2022年一类片区全口径10449」误置于「2023年」行（年份错位一年，与京津沪的数据年口径不一致），已按数据年口径重排（2022=10449官方、2023≈10876按全省增速9167/8807估算）；其余城市若采用相同锚定方式亦可能存在同类错位，待逐城核查。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>一、数据完整性说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>为方便查阅，本表 1989–2033 各城市均已填满（1989 起为本次补全）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ① 北京/上海：1989–2005 为真实统计年鉴序列（北京1989–1991为城镇单位在岗口径估算；上海为前瞻数据库序列按2006锚点缩放衔接）；2006–2023 为官方实际值；2024–2033 按 2% 前瞻估算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：早年（1989–2017）为按真实全口径锚点回溯的估算序列；2018 起逐年采用人社局/统计公报公布的真实全口径城镇单位就业人员月平均工资；2024–2033 按 2% 前瞻。⚠ 原表误用「城镇非私营单位在岗职工平均工资」导致整列偏高，已于 2026-10 按真实全口径锚点整体回缩校正（天津 2025=8,634 经津人社局发〔2026〕5号核实）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ③ 陕西官方截止 2022（2023 基数用 2022 全口径），2023 为 2022×1.02 的展示值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>二、重要：生成工作簿时的使用规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>脚本生成测算表时：2006–2023（官方截止年及之前）采用本表静态值；2024 年及以后一律按“社平增幅”参数</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>（默认 2%）活公式实时推算，与本表展示值无关。故修改参数区“社平增幅”，未来年份与退休金会即时联动重算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>三、数据来源与免责</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  广东（锚点2023=9,167）：粤人社发〔2024〕33号：2023全省全口径月均（含广州/深圳/省直一类片区）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  浙江（锚点2023=8,020）：浙人社发〔2023〕60号：省平96237/年</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  江苏（锚点2023=8,014）：2023上限24042=300%，倒推省全口径月均</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  重庆（锚点2023=6,863）：渝人社发〔2023〕48号：82348/年</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  天津（锚点2023=8,355；2024=8,540；2025=8,634）：津人社局发〔2026〕5号/〔2025〕6号 全市职工月均（=全口径，且 8,634×3=25,902 即 2026 缴费基数上限，口径自洽）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  湖北（锚点2023=7,040）：鄂人社发〔2023〕30号：第1档月标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  陕西（锚点2022=7,028.67）：陕人社函〔2023〕469号：84344/年（2023基数用2022全口径）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>深圳（2022一类全口径=10,449 官方粤人社发〔2023〕22号；2023≈10,876 按全省增速9167/8807估算；2024养老金计发基数11,181 深人社发〔2024〕57号）：原表将2022值误置于2023行，已校正为数据年口径。注：深圳作为计划单列市未单发分市全口径，采用一类片区（广州/深圳/省直）值；其养老金计发基数(2023≈10,795、2024=11,181)与全口径接近。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  沈阳（锚点2023=7,121）：辽人社〔2024〕12号：2023全省全口径月均（沈阳执行辽宁）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  大连（锚点2023=7,121）：辽人社〔2024〕12号：2023全省全口径月均（大连执行辽宁）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  四川（锚点2023=7,518.33）：川人社办发〔2024〕48号：2023全省全口径90220/年（2024基数上限22,555=300%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 缓存为通用参考，可能与您本人社保局系统的精确社平/缴费基数有出入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>请计算后务必以参保地社保局公布的“全口径社平工资”核实；可在生成的测算表中直接修改对应年份社平，结果即时重算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖城市：生成脚本会提示联网查询“全口径城镇单位就业人员月平均工资”，或由用户手动填入 manual_sheping。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -746,7 +543,7 @@
         <v>1989</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>162.58</v>
+        <v>544.5</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>171.09</v>
@@ -790,7 +587,7 @@
         <v>1990</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>212.33</v>
+        <v>609.8</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>208.66</v>
@@ -834,7 +631,7 @@
         <v>1991</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>220.92</v>
+        <v>683</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>232.23</v>
@@ -878,7 +675,7 @@
         <v>1992</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>283.5</v>
+        <v>765</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>295.42</v>
@@ -922,7 +719,7 @@
         <v>1993</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>376.92</v>
+        <v>856.8</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>357.4</v>
@@ -966,7 +763,7 @@
         <v>1994</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>545</v>
+        <v>959.6</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>454.2</v>
@@ -1010,7 +807,7 @@
         <v>1995</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>678.67</v>
+        <v>1074.7</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>594.42</v>
@@ -1054,7 +851,7 @@
         <v>1996</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>798.25</v>
+        <v>1203.7</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>742.55</v>
@@ -1098,7 +895,7 @@
         <v>1997</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>918.25</v>
+        <v>1348.1</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>868.77</v>
@@ -1142,7 +939,7 @@
         <v>1998</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1023.75</v>
+        <v>1509.9</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1032.64</v>
@@ -1186,7 +983,7 @@
         <v>1999</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1148.17</v>
+        <v>1691.1</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>1265.41</v>
@@ -1230,7 +1027,7 @@
         <v>2000</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1310.5</v>
+        <v>1894</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>1409.13</v>
@@ -1274,7 +1071,7 @@
         <v>2001</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1507.67</v>
+        <v>2121.3</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>1656.26</v>
@@ -1318,7 +1115,7 @@
         <v>2002</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1727.33</v>
+        <v>2375.9</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>1821.88</v>
@@ -1362,7 +1159,7 @@
         <v>2003</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2003.75</v>
+        <v>2661</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>2076.24</v>
@@ -1406,7 +1203,7 @@
         <v>2004</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2362.33</v>
+        <v>2980.3</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>2287.71</v>
@@ -1450,7 +1247,7 @@
         <v>2005</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2734</v>
+        <v>3337.9</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>2611.65</v>
@@ -1494,7 +1291,7 @@
         <v>2006</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>3008</v>
+        <v>3738.5</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>3132</v>
@@ -1538,7 +1335,7 @@
         <v>2007</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>3322</v>
+        <v>4149.7</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>3748</v>
@@ -1582,7 +1379,7 @@
         <v>2008</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>3726</v>
+        <v>4606.2</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>4344</v>
@@ -1626,7 +1423,7 @@
         <v>2009</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>4037</v>
+        <v>5112.9</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>4861</v>
@@ -1670,7 +1467,7 @@
         <v>2010</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>4201</v>
+        <v>5675.4</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>5510</v>
@@ -1714,7 +1511,7 @@
         <v>2011</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>4672</v>
+        <v>6299.7</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>6300</v>
@@ -1758,7 +1555,7 @@
         <v>2012</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>5223</v>
+        <v>6992.7</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>6556</v>
@@ -1802,7 +1599,7 @@
         <v>2013</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>5793</v>
+        <v>7761.9</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>7576</v>
@@ -1846,7 +1643,7 @@
         <v>2014</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>6463</v>
+        <v>8616.67</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>8354</v>
@@ -1890,7 +1687,7 @@
         <v>2015</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>7086</v>
+        <v>9422.75</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>9098</v>
@@ -1934,7 +1731,7 @@
         <v>2016</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>7706</v>
+        <v>10229.08</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>9995</v>
@@ -1978,7 +1775,7 @@
         <v>2017</v>
       </c>
       <c r="B30" t="n">
-        <v>8467</v>
+        <v>11249.5</v>
       </c>
       <c r="C30" t="n">
         <v>10816</v>
@@ -2022,7 +1819,7 @@
         <v>2018</v>
       </c>
       <c r="B31" t="n">
-        <v>7855</v>
+        <v>12486.92</v>
       </c>
       <c r="C31" t="n">
         <v>8765</v>
@@ -2066,7 +1863,7 @@
         <v>2019</v>
       </c>
       <c r="B32" t="n">
-        <v>8847</v>
+        <v>14433.75</v>
       </c>
       <c r="C32" t="n">
         <v>9580</v>
@@ -2110,7 +1907,7 @@
         <v>2020</v>
       </c>
       <c r="B33" t="n">
-        <v>9407</v>
+        <v>9910</v>
       </c>
       <c r="C33" t="n">
         <v>10338</v>
@@ -2154,7 +1951,7 @@
         <v>2021</v>
       </c>
       <c r="B34" t="n">
-        <v>10628</v>
+        <v>10534</v>
       </c>
       <c r="C34" t="n">
         <v>11396</v>
@@ -2198,7 +1995,7 @@
         <v>2022</v>
       </c>
       <c r="B35" t="n">
-        <v>11297</v>
+        <v>11082</v>
       </c>
       <c r="C35" t="n">
         <v>12183</v>
@@ -2242,7 +2039,7 @@
         <v>2023</v>
       </c>
       <c r="B36" t="n">
-        <v>11761</v>
+        <v>11525</v>
       </c>
       <c r="C36" t="n">
         <v>12307</v>
@@ -2286,7 +2083,7 @@
         <v>2024</v>
       </c>
       <c r="B37" t="n">
-        <v>11996.22</v>
+        <v>11883</v>
       </c>
       <c r="C37" t="n">
         <v>12553.14</v>
@@ -2330,7 +2127,7 @@
         <v>2025</v>
       </c>
       <c r="B38" t="n">
-        <v>12236.14</v>
+        <v>12120.66</v>
       </c>
       <c r="C38" t="n">
         <v>12804.2</v>
@@ -2374,7 +2171,7 @@
         <v>2026</v>
       </c>
       <c r="B39" t="n">
-        <v>12480.87</v>
+        <v>12363.07</v>
       </c>
       <c r="C39" t="n">
         <v>13060.29</v>
@@ -2418,7 +2215,7 @@
         <v>2027</v>
       </c>
       <c r="B40" t="n">
-        <v>12730.48</v>
+        <v>12610.33</v>
       </c>
       <c r="C40" t="n">
         <v>13321.49</v>
@@ -2462,7 +2259,7 @@
         <v>2028</v>
       </c>
       <c r="B41" t="n">
-        <v>12985.09</v>
+        <v>12862.54</v>
       </c>
       <c r="C41" t="n">
         <v>13587.92</v>
@@ -2506,7 +2303,7 @@
         <v>2029</v>
       </c>
       <c r="B42" t="n">
-        <v>13244.8</v>
+        <v>13119.79</v>
       </c>
       <c r="C42" t="n">
         <v>13859.68</v>
@@ -2550,7 +2347,7 @@
         <v>2030</v>
       </c>
       <c r="B43" t="n">
-        <v>13509.69</v>
+        <v>13382.19</v>
       </c>
       <c r="C43" t="n">
         <v>14136.87</v>
@@ -2594,7 +2391,7 @@
         <v>2031</v>
       </c>
       <c r="B44" t="n">
-        <v>13779.89</v>
+        <v>13649.83</v>
       </c>
       <c r="C44" t="n">
         <v>14419.61</v>
@@ -2638,7 +2435,7 @@
         <v>2032</v>
       </c>
       <c r="B45" t="n">
-        <v>14055.48</v>
+        <v>13922.82</v>
       </c>
       <c r="C45" t="n">
         <v>14708</v>
@@ -2682,7 +2479,7 @@
         <v>2033</v>
       </c>
       <c r="B46" t="n">
-        <v>14336.59</v>
+        <v>14201.28</v>
       </c>
       <c r="C46" t="n">
         <v>15002.16</v>
@@ -2719,6 +2516,121 @@
       </c>
       <c r="N46" t="n">
         <v>8680.459999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>各地“社平工资”（养老金计发基数口径）缓存表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>用途：本表为「养老金测算」skill 预缓存数据，供计算缴费指数与退休金时按“待遇领取地社平”查表。本表“社平”=养老金公式里的“退休时上年度社平工资”，即人社公布的【养老金计发基数】。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>口径铁律（三种“社平”的区别，务必分清）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 城镇非私营单位在岗职工平均工资——早年(2020前)养老金公式的“社平”，数值最高；② 全口径城镇单位就业人员平均工资——仅用于核定社保缴费基数上下限，★不是★养老金公式口径；③ 养老金计发基数——人社每年公布的、真正用于养老金公式的“退休时社平”，2020年起各地普遍单独公布。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本表采用：2020年及以后 = 养老金计发基数（人社公布）；2020年以前 = 城镇非私营单位在岗职工平均工资（统计年鉴）。⚠ 历史坑：本表曾先后误用“非私营”和“全口径”两种错误口径，均非养老金公式正确口径，现已按计发基数校正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>一、数据完整性说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本表 1989–2033 各城市均已填满。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 北京（已校正）：2020–2024 为真实养老金计发基数（京人社发各年文件：2020=9910、2021=10534、2022=11082、2023=11525、2024=11883）；2025–2033 按 2% 前瞻；2014–2019 为真实非私营在岗（年值÷12）；2006–2013、1989–2005 为按锚点回溯的估算（仅填表完整，以社保局为准）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 其余 11 城（四川/广东/浙江/江苏/重庆/天津/湖北/陕西/深圳/沈阳/大连）：目前仍为“全口径城镇单位就业人员平均工资”（错误口径），待逐个查真实养老金计发基数后校正。其中天津/广东/深圳/四川的计发基数已查到（天津2023=9016、2024=9232；广东2023=9028、2024=9307；深圳2024=11181；四川2023=8079、2024=8321），尚未回填本表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>二、生成工作簿时的使用规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  脚本生成测算表时：≤ OFFICIAL_LAST_YEAR（2024）采用本表静态值；2024 年以后的年份一律按“社平增幅”参数（默认 2%）推算，与本表展示值无关。故修改参数区“社平增幅”，未来年份与退休金会即时联动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>三、数据来源与免责</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  北京（计发基数）：京人社发〔2022〕14号(2022=11082)、〔2024〕16号(2024=11883)、2023=11525、2021=10534、2020=9910（北京人社局历年通告）；2020前非私营在岗取自北京统计年鉴/《中国统计年鉴》。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>⚠ 缓存为通用参考，可能与您本人社保局系统的精确值有出入。请计算后务必以参保地社保局公布的“养老金计发基数”核实；可在生成的测算表中直接修改对应年份社平，结果即时重算。本表为规划辅助，非官方核算。</t>
+        </is>
       </c>
     </row>
   </sheetData>
